--- a/docs/requirements/Application Rationalization Agent Requirements - filled.xlsx
+++ b/docs/requirements/Application Rationalization Agent Requirements - filled.xlsx
@@ -28,10 +28,10 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -88,13 +88,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Ingest structured portfolio exports dropped into a watched folder - CMDB/ServiceNow app table, SSO sign-in logs (Okta/Entra), AP and expense-report line items, contract/subscription registers - auto-detect each file's schema, map its columns onto the canonical application-record model, and emit a load report showing rows accepted, rows rejected with the reason, and any source column the agent could not map (which becomes a human decision, not a silent drop). [MVP]</t>
+          <t>(Step 2) Ingest structured portfolio exports dropped into a watched folder - CMDB/ServiceNow app table, SSO sign-in logs (Okta/Entra), AP and expense-report line items, contract/subscription registers - auto-detect each file's schema, map its columns onto the canonical application-record model, and emit a load report showing rows accepted, rows rejected with the reason, and any source column the agent could not map (which becomes a human decision, not a silent drop). [MVP]</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Deduplicate and canonicalize inconsistent application names across sources (e.g. 'MSFT O365', 'Office 365 E3', 'Microsoft 365 - Finance') by clustering on name, vendor, and URL/domain similarity, then resolve each cluster to a single canonical app record carrying a match confidence score and the list of source rows it absorbed. Clusters below the confidence threshold go to a human-review queue instead of being merged silently. [MVP]</t>
+          <t>(Step 2) Deduplicate and canonicalize inconsistent application names across sources (e.g. 'MSFT O365', 'Office 365 E3', 'Microsoft 365 - Finance') by clustering on name, vendor, and URL/domain similarity, then resolve each cluster to a single canonical app record carrying a match confidence score and the list of source rows it absorbed. Clusters below the confidence threshold go to a human-review queue instead of being merged silently. [MVP]</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Surface shadow IT by diffing SaaS spend found in AP/expense data and active sign-in activity found in SSO logs against the sanctioned CMDB inventory. Output the apps that are in use or being paid for but not governed, each with its evidence trail (which source, which cost line, which users) and an estimated annual run-rate - typically the largest single block of unmanaged spend in a 15% reduction exercise. [MVP]</t>
+          <t>(Steps 1-2) Surface shadow IT by diffing SaaS spend found in AP/expense data and active sign-in activity found in SSO logs against the sanctioned CMDB inventory. Output the apps that are in use or being paid for but not governed, each with its evidence trail (which source, which cost line, which users) and an estimated annual run-rate - typically the largest single block of unmanaged spend in a 15% reduction exercise. [MVP]</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Extend REQ 1: scan an application document repository (SharePoint or an equivalent folder) and extract meaningful data points from architecture diagrams, contracts, SOWs, security reviews, and support handbooks into structured fields - keeping a citation back to source document and page for every value extracted, so nothing entering the record is unattributable. [MVP against a local/exported document folder; STRETCH for a live SharePoint connector - SharePoint is sign-in gated and was not reachable from the hackathon environment]</t>
+          <t>(Step 2) Extend REQ 1: scan an application document repository (SharePoint or an equivalent folder) and extract meaningful data points from architecture diagrams, contracts, SOWs, security reviews, and support handbooks into structured fields - keeping a citation back to source document and page for every value extracted, so nothing entering the record is unattributable. [MVP against a local/exported document folder; STRETCH for a live SharePoint connector - SharePoint is sign-in gated and was not reachable from the hackathon environment]</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Build an application dependency map from interface inventories, integration/middleware configuration, and narrative descriptions in the scanned documents; emit a directed dependency edge list with confidence per edge, so that any later 'retire' recommendation can be tested for downstream breakage rather than issued blind. [STRETCH] [DATA GAP: no interface or integration inventory in the Novant extract - needs synthetic dependency data]</t>
+          <t>(Step 2) Build an application dependency map from interface inventories, integration/middleware configuration, and narrative descriptions in the scanned documents; emit a directed dependency edge list with confidence per edge - directly serving step 2's 'map technical dependencies and integrations', and the prerequisite for testing any later 'retire' recommendation for downstream breakage. [STRETCH] [DATA GAP: no interface or integration inventory in the Novant extract - needs synthetic dependency data]</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Inventory AI tools and agents as a first-class category - standalone copilots and chatbots, plus AI features embedded inside SaaS products the organization already licenses - classifying each by the capability it delivers and the underlying model provider. These rarely appear in the CMDB and overlap heavily, and the hackathon prompt calls them out explicitly. [MVP]</t>
+          <t>(Steps 1-2) Inventory AI tools and agents as a first-class category - standalone copilots and chatbots, plus AI features embedded inside SaaS products the organization already licenses - classifying each by the capability it delivers and the underlying model provider. These rarely appear in the CMDB and overlap heavily, and the hackathon prompt calls them out explicitly. [MVP]</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Extend REQ 2: score every application record for completeness against the fields the scoring model actually consumes, and rank the resulting gap list by how much each missing field would move that app's final disposition - so the team chases the handful of fields that change answers rather than trying to complete every field on every app. [MVP]</t>
+          <t>(Step 2) Extend REQ 2: score every application record for completeness against the fields the scoring model actually consumes, and rank the resulting gap list by how much each missing field would move that app's final disposition - so the team chases the handful of fields that change answers rather than trying to complete every field on every app. [MVP]</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Extend REQ 3: compile the enriched, deduplicated portfolio into a single consolidated application register - one row per canonical app, all critical data points, provenance and confidence attached - as the single artifact every downstream score, chart, and slide is computed from. [MVP]</t>
+          <t>(Step 2) Extend REQ 3: compile the enriched, deduplicated portfolio into a single consolidated application register - one row per canonical app, all critical data points, provenance and confidence attached - as the single artifact every downstream score, chart, and slide is computed from. [MVP]</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>For each missing or low-confidence field, generate a targeted question set addressed to the named application owner (not a generic 200-question survey), and fold the answers back into the record marked as 'owner-attested' rather than 'system-of-record', so the provenance of a human answer stays visible. [STRETCH]</t>
+          <t>(Steps 1-2) For each missing or low-confidence field, generate a targeted question set addressed to the named application owner (not a generic 200-question survey), and fold the answers back into the record marked as 'owner-attested' rather than 'system-of-record', so the provenance of a human answer stays visible. Also captures step 1's business objectives and pain points from the owner in structured form. [STRETCH]</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Enrich each canonical app with vendor and product metadata - legal vendor entity, product family, deployment model (SaaS / hosted / on-prem), version installed vs version currently vendor-supported - and flag every case where the installed version has fallen behind support.</t>
+          <t>(Step 2) Enrich each canonical app with vendor and product metadata - legal vendor entity, product family, deployment model (SaaS / hosted / on-prem), version installed vs version currently vendor-supported - and flag every case where the installed version has fallen behind support.</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Extract commercial terms from contract and order-form PDFs into structured fields: annual contract value, term start and end, renewal and auto-renewal notice windows, license metric (per-user / per-bed / enterprise / consumption), true-up and early-termination clauses - each with a citation to the clause it came from. Emit a renewal calendar showing which decisions carry a real deadline in the next 12 months. [MVP] [DATA GAP: contract data missing from the Novant extract - synthetic contracts needed]</t>
+          <t>(Steps 2, 5) Extract commercial terms from contract and order-form PDFs into structured fields: annual contract value, term start and end, renewal and auto-renewal notice windows, license metric (per-user / per-bed / enterprise / consumption), true-up and early-termination clauses - each with a citation to the clause it came from. Emit a renewal calendar showing which decisions carry a real deadline in the next 12 months, which is what drives roadmap sequencing at step 5. [MVP] [DATA GAP: contract data missing from the Novant extract - synthetic contracts needed]</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Determine hosting, end-of-life, and support status per application (vendor EOL/EOS dates, underlying OS and database support status, platform supportability) and convert it into a technical obsolescence flag with the date at which the risk becomes real - which is what turns 'old' into a scheduling decision.</t>
+          <t>(Step 2) Determine hosting, end-of-life, and support status per application (vendor EOL/EOS dates, underlying OS and database support status, platform supportability) and convert it into a technical obsolescence flag with the date at which the risk becomes real - which is what turns 'old' into a scheduling decision.</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Resolve an accountable business owner and technical owner for every application by triangulating CMDB assignment groups, the cost centre carrying the spend line, and the heaviest sign-in users from SSO. Where no owner can be established, mark the app orphaned - orphaned plus low usage is consistently the highest-yield elimination candidate and the easiest to defend.</t>
+          <t>(Steps 1-2) Resolve an accountable business owner and technical owner for every application by triangulating CMDB assignment groups, the cost centre carrying the spend line, and the heaviest sign-in users from SSO - satisfying step 1's 'identify stakeholders' as a derived output rather than a manual exercise. Where no owner can be established, mark the app orphaned; orphaned plus low usage is consistently the highest-yield elimination candidate and the easiest to defend.</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Tag every application against a business capability model (for a health system: patient access, revenue cycle, clinical documentation, imaging, pharmacy, supply chain, HR, finance, analytics) with primary and secondary capability tags plus a confidence score, inferred from product documentation and app descriptions. This tagging is the foundation for all redundancy detection downstream - if it is wrong, the overlap findings are wrong. [MVP] [DATA GAP: no capability field in the Novant extract] [ASSUMPTION: we adopt an existing published health-system capability taxonomy rather than authoring one on build day - Bina to confirm]</t>
+          <t>(Step 3) Tag every application against a business capability model (for a health system: patient access, revenue cycle, clinical documentation, imaging, pharmacy, supply chain, HR, finance, analytics) with primary and secondary capability tags plus a confidence score, inferred from product documentation and app descriptions - step 3's 'map applications to business capabilities'. This tagging is the foundation for all redundancy detection downstream: if it is wrong, the overlap findings are wrong. [MVP] [DATA GAP: no capability field in the Novant extract] [ASSUMPTION: we adopt an existing published health-system capability taxonomy rather than authoring one on build day - Bina to confirm]</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Reconstruct total cost of ownership where source data carries only licence cost: subscription/licence + support and maintenance + infrastructure/hosting + internal FTE support effort, applying documented estimation rules and labelling each component as actual, allocated, or estimated so a CFO can see immediately which figures are defensible and which are modelled. [MVP] [DATA GAP: most cost fields missing from the Novant extract] [Worth cross-checking the component breakdown against Infotech '05-Application-TCO-Calculator.xlsx' that Bina shared - that file was not readable from this session]</t>
+          <t>(Steps 2-3) Reconstruct total cost of ownership where source data carries only licence cost: subscription/licence + support and maintenance + infrastructure/hosting + internal FTE support effort, applying documented estimation rules and labelling each component as actual, allocated, or estimated so a CFO can see immediately which figures are defensible and which are modelled. [MVP] [DATA GAP: most cost fields missing from the Novant extract] [Worth cross-checking the component breakdown against Infotech '05-Application-TCO-Calculator.xlsx' that Bina shared - that file was not readable from this session]</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Score business value on a normalized 1-5 scale from weighted sub-factors - criticality to patient care and to revenue, breadth of use (active users vs licences purchased), process centrality, and owner-stated strategic importance - and emit the score together with each sub-factor's contribution, so a stakeholder argues with an input rather than with a black-box number. [MVP]</t>
+          <t>(Step 3) Score business value on a normalized 1-5 scale from weighted sub-factors - criticality to patient care and to revenue, breadth of use (active users vs licences purchased), process centrality, and owner-stated strategic importance - and emit the score together with each sub-factor's contribution, so a stakeholder argues with an input rather than with a black-box number. [MVP]</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Score technical fit and health from supportability (version currency, EOL proximity), architecture fit (integration pattern, cloud readiness, customization debt), operational stability (incident/ticket volume where available), and vendor viability - emitting the score plus the top two drivers pulling it down, which are the inputs to any 'invest' remediation plan. [MVP]</t>
+          <t>(Step 3) Score technical fit and health from supportability (version currency, EOL proximity), architecture fit (integration pattern, cloud readiness, customization debt), operational stability (incident/ticket volume where available), and vendor viability - emitting the score plus the top two drivers pulling it down, which are the inputs to any 'invest' remediation plan. [MVP]</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Score cost efficiency as TCO against value delivered: cost per active user benchmarked against peer applications in the same capability, and licensed-vs-active seat waste. Report unused-licence spend as its own explicit dollar line item - it is the fastest credible saving available against a 15% reduction target and needs no migration project. [MVP]</t>
+          <t>(Step 3) Score cost efficiency as TCO against value delivered: cost per active user benchmarked against peer applications in the same capability, and licensed-vs-active seat waste. Report unused-licence spend as its own explicit dollar line item - it is the fastest credible saving available against a 15% reduction target and needs no migration project. [MVP]</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Score risk on two axes kept deliberately separate rather than blended: technical risk (unsupported versions, single points of failure, no DR/backup, single-vendor concentration) and business/compliance risk (PHI and HIPAA exposure, data residency, SOC 2 / HITRUST posture, vendor financial viability, contractual lock-in). Emit both scores plus the specific findings behind each. [MVP] [DATA GAP: technical and business risk fields missing from the Novant extract - synthetic risk attributes needed]</t>
+          <t>(Step 3) Score risk on two axes kept deliberately separate rather than blended: technical risk (unsupported versions, single points of failure, no DR/backup, single-vendor concentration) and business/compliance risk (PHI and HIPAA exposure, data residency, SOC 2 / HITRUST posture, vendor financial viability, contractual lock-in). Emit both scores plus the specific findings behind each. [MVP] [DATA GAP: technical and business risk fields missing from the Novant extract - synthetic risk attributes needed]</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Detect functional redundancy by grouping applications sharing a business capability tag and comparing feature coverage, user overlap, and cost - emitting ranked overlap clusters with a recommended survivor, the reason it survives, and the consolidation saving available. Target output reads like: 'four products cover secure clinical messaging; 2,100 of 3,400 users hold two or more; consolidating to one saves $X annually.' [MVP - this is the demo's money slide]</t>
+          <t>(Steps 3-4) Detect functional redundancy by grouping applications sharing a business capability tag and comparing feature coverage, user overlap, and cost - emitting ranked overlap clusters with a recommended survivor, the reason it survives, and the consolidation saving available. This is step 4's 'develop consolidation recommendations'. Target output reads like: 'four products cover secure clinical messaging; 2,100 of 3,400 users hold two or more; consolidating to one saves $X annually.' [MVP - this is the demo's money slide]</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Detect duplicate capability among AI tools and agents specifically, including the case where a capability being bought standalone is already entitled inside an existing enterprise licence - output the finding with the already-paid-for alternative named, since that is a saving with no functional loss at all. [MVP]</t>
+          <t>(Steps 3-4) Detect duplicate capability among AI tools and agents specifically, including the case where a capability being bought standalone is already entitled inside an existing enterprise licence - output the finding with the already-paid-for alternative named, since that is a saving with no functional loss at all. [MVP]</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Extend REQ 4: place each application into its disposition category (invest / consolidate / replace / retire) from business value and technical health, with cost, risk, and redundancy as modifiers - and emit for each app a written rationale in consultant language that cites the specific scores and evidence that drove the placement, plus a confidence level. The rationale, not the quadrant, is the deliverable. [MVP]</t>
+          <t>(Step 4) Extend REQ 4: place each application into its disposition category from business value and technical health, with cost, risk, and redundancy as modifiers - and emit for each app a written rationale in consultant language that cites the specific scores and evidence that drove the placement, plus a confidence level. The rationale, not the category, is the deliverable. [MVP] [See the step-4 vocabulary note on the Notes sheet: Ryo's REQ 4 uses invest/consolidate/replace/retire, slide 13 uses retain/replace/retire - needs a team decision]</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Where evidence is thin, state it: mark the recommendation low-confidence and name the single piece of missing data that would resolve it, rather than presenting a guess at the same confidence as a well-evidenced finding. [MVP - the credibility feature; a tool that confidently recommends retiring an app on no data is worse than no tool]</t>
+          <t>(Step 4) Where evidence is thin, state it: mark the recommendation low-confidence and name the single piece of missing data that would resolve it, rather than presenting a guess at the same confidence as a well-evidenced finding. [MVP - the credibility feature; a tool that confidently recommends retiring an app on no data is worse than no tool]</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Test every 'retire' and 'consolidate' recommendation against the dependency map and the renewal calendar, and defer or downgrade any recommendation that would break a dependent system or trigger an early-termination penalty exceeding the saving. Output these separately as a constrained list with the blocking reason and the date the constraint lifts. [STRETCH]</t>
+          <t>(Steps 4-5) Test every 'retire' and 'consolidate' recommendation against the dependency map and the renewal calendar, and defer or downgrade any recommendation that would break a dependent system or trigger an early-termination penalty exceeding the saving. Output these separately as a constrained list with the blocking reason and the date the constraint lifts. [STRETCH]</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Let a human reviewer override any disposition with a recorded reason, and re-run the affected downstream calculations - savings roll-up, roadmap sequence, capability coverage - so the deck never contradicts the override. [STRETCH]</t>
+          <t>(Step 4) Let a human reviewer override any disposition with a recorded reason, and re-run the affected downstream calculations - savings roll-up, roadmap sequence, capability coverage - so the deck never contradicts the override. [STRETCH]</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Sequence approved dispositions into a phased roadmap (wave 1 quick wins 0-3 months, wave 2 3-9 months, wave 3 9-18 months) ordered by saving size, implementation effort, dependency prerequisites, and contract renewal dates - output as a wave plan showing cumulative savings realized per quarter against the CIO's 15% reduction target. [MVP]</t>
+          <t>(Step 5) Sequence approved dispositions into a phased roadmap (wave 1 quick wins 0-3 months, wave 2 3-9 months, wave 3 9-18 months) ordered by saving size, implementation effort, dependency prerequisites, and contract renewal dates - step 5's 'prioritize initiatives and timeline'. Output as a wave plan showing cumulative savings realized per quarter against the CIO's 15% reduction target. [MVP]</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Quantify savings per recommendation with the arithmetic shown and the assumptions stated (recurring vs one-time, gross vs net of migration cost, realization lag from decision to saved dollar), then roll up to a portfolio figure expressed as a confidence range rather than a single false-precision number. [MVP]</t>
+          <t>(Step 5) Quantify savings per recommendation with the arithmetic shown and the assumptions stated (recurring vs one-time, gross vs net of migration cost, realization lag from decision to saved dollar), then roll up to a portfolio figure expressed as a confidence range rather than a single false-precision number. [MVP]</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Business case / deliverables</t>
+          <t>Roadmap &amp; sequencing</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Generate the stakeholder deliverable set straight from the analysis - executive summary, disposition matrix, redundancy findings, savings roll-up, phased roadmap - as an exportable document or slide pack a consultant could take into a client steering committee with light editing rather than a rewrite. [MVP]</t>
+          <t>(Step 5) Estimate the resource requirement per initiative and per wave - implementation effort band, skills needed, owner teams involved, and expected elapsed duration - so the roadmap is capacity-tested rather than a wish list, satisfying step 5's 'define metrics and resource requirements'. [STRETCH]</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Generate a per-application business case one-pager for contested decisions (the apps an owner will fight for): current cost, recommended disposition, rationale, proposed alternative, migration effort, and the risk of doing nothing. [STRETCH]</t>
+          <t>(Step 5) Generate the stakeholder deliverable set straight from the analysis - executive summary, disposition matrix, redundancy findings, savings roll-up, phased roadmap - as an exportable document or slide pack a consultant could take into a client steering committee with light editing rather than a rewrite. [MVP]</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Draft owner-facing change communications per disposition - what is changing, why, what replaces it, what the owner must do and by when. Stakeholder resistance rather than weak analysis is what actually stalls rationalization programs. [STRETCH]</t>
+          <t>(Step 5) Generate a per-application business case one-pager for contested decisions (the apps an owner will fight for): current cost, recommended disposition, rationale, proposed alternative, migration effort, and the risk of doing nothing. [STRETCH]</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Data collection/UI</t>
+          <t>Business case / deliverables</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Extend REQ 5: alongside the document and link upload surface, provide a portfolio workspace - filterable application register, disposition matrix view, redundancy clusters, savings tracker, and drill-through from any figure to the underlying application records. [MVP for upload + register table + disposition view; STRETCH for the full interactive dashboard]</t>
+          <t>(Steps 5-6) Draft owner-facing change communications per disposition - what is changing, why, what replaces it, what the owner must do and by when. Stakeholder resistance rather than weak analysis is what actually stalls rationalization programs, and this is where step 6's 'coordinate teams' begins. [STRETCH]</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Data collection/UI</t>
+          <t>Execution &amp; tracking</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Expose the human-review queue in the UI as a work list - ambiguous name matches, low-confidence dispositions, missing critical fields, orphaned apps - so a consultant clears exceptions in minutes instead of auditing the whole portfolio. [MVP]</t>
+          <t>(Step 6) Generate a per-application decommission or migration runbook from the disposition, dependency, and contract data: prerequisite steps, data retention and archival obligations, integration cutover points, the licence-termination notice that must be served and by when, user communication and training needs, and rollback criteria. Emit as an assignable task list a PMO can load into a plan, not as prose. [MVP for retire/consolidate runbooks; STRETCH for migration runbooks]</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Trust &amp; traceability</t>
+          <t>Execution &amp; tracking</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Maintain field-level provenance for every value in the application register (source system or document, extraction timestamp, confidence, AI-inferred vs system-of-record) and expose it on drill-down, so any number in the final deck can be traced to its origin the moment a client challenges it. [MVP]</t>
+          <t>(Step 6) Track execution progress against the wave plan by ingesting periodic status updates (PMO tracker export, ticket system, or owner attestation) and reporting per-initiative status, slipped milestones, and the savings at risk behind each slip - with a portfolio view answering the only question the CIO asks: is the 15% still on track, and if not, where did it go. [MVP - demoable by feeding the tool two snapshots of the same portfolio]</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Trust &amp; traceability</t>
+          <t>Execution &amp; tracking</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Never silently invent a value: where the agent estimates or infers a field, label it inferred, record the basis for the inference, and keep inferred values visually distinct from sourced values in every output and export. [MVP]</t>
+          <t>(Step 6) Detect execution conflicts across in-flight initiatives - two waves touching the same integration, one owner team overloaded in a single quarter, a retirement scheduled before its replacement goes live - and raise each as a sequencing exception with a proposed re-order, so step 6's coordination problem is surfaced rather than discovered late.</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,162 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>Execution &amp; tracking</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>(Step 6) Summarize execution blockers into a steering-committee escalation brief: what is stalled, who owns it, the decision being asked for, the options with their trade-offs, and the cost of continued delay expressed in deferred savings. [STRETCH]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Monitoring &amp; optimization</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>(Step 7) Measure realized savings against projection for every executed recommendation by re-reading current spend, licence, and contract data after execution, and report variance per initiative and per portfolio - naming the specific recommendations that under-delivered and why (licences never actually terminated, contract auto-renewed through the notice window, capability re-purchased elsewhere). [MVP - the most credible thing the tool can put in front of a CIO, and the check almost nobody performs]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Monitoring &amp; optimization</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>(Step 7) Detect portfolio drift after rationalization: retired applications still showing sign-in activity or spend, new purchases that re-introduce a capability just consolidated, and licence counts creeping back up - raised as alerts naming the originating cost centre, so the portfolio does not silently re-bloat to where it started. [MVP]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Monitoring &amp; optimization</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>(Steps 5, 7) Define and baseline the rationalization KPI set up front - application count, total spend, spend per business capability, redundancy ratio, share of apps on vendor-supported versions, orphaned app count - then report the trend each cycle against that baseline, so step 7's 'measure improvements' is measured rather than asserted. [MVP]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Monitoring &amp; optimization</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>(Step 7) Feed measured outcomes back into the model: where realized savings or migration effort consistently diverged from the estimate, surface the systematic bias and propose a recalibration of the scoring weights or estimation rules, recording what changed and why - step 7's 'adjust strategy based on outcomes', and what makes successive cycles more accurate instead of repeating the same error. [STRETCH]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Monitoring &amp; optimization</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>(Step 7) Re-run the full assessment on a schedule against refreshed source data and report only what changed since the last cycle: applications that appeared, dispositions that flipped and why, contracts newly inside their notice window, and drift alerts outstanding. This is what turns rationalization into an operating cadence instead of a one-off consulting engagement - and it is the difference between shipping a tool and shipping a report. [STRETCH - but it is the product story]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Data collection/UI</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>(All steps) Extend REQ 5: alongside the document and link upload surface, provide a portfolio workspace - filterable application register, disposition matrix view, redundancy clusters, savings tracker against target, execution status by wave, and drill-through from any figure to the underlying application records. [MVP for upload + register table + disposition view; STRETCH for the full interactive dashboard]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Data collection/UI</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>(Steps 2-4) Expose the human-review queue in the UI as a work list - ambiguous name matches, low-confidence dispositions, missing critical fields, orphaned apps - so a consultant clears exceptions in minutes instead of auditing the whole portfolio. [MVP]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
           <t>Trust &amp; traceability</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Make the scoring model configurable - weights per scoring dimension and the disposition thresholds - and record which weight set produced a given output, so the same tool can be re-pointed at another client's priorities without re-engineering and prior conclusions remain reproducible. [STRETCH]</t>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>(All steps) Maintain field-level provenance for every value in the application register (source system or document, extraction timestamp, confidence, AI-inferred vs system-of-record) and expose it on drill-down, so any number in the final deck can be traced to its origin the moment a client challenges it. [MVP]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Trust &amp; traceability</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>(All steps) Never silently invent a value: where the agent estimates or infers a field, label it inferred, record the basis for the inference, and keep inferred values visually distinct from sourced values in every output and export. [MVP]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Trust &amp; traceability</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>(Steps 3-4) Make the scoring model configurable - weights per scoring dimension and the disposition thresholds - and record which weight set produced a given output, so the same tool can be re-pointed at another client's priorities without re-engineering and prior conclusions stay reproducible. [STRETCH]</t>
         </is>
       </c>
     </row>
@@ -1135,11 +1285,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="125" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,30 +1301,38 @@
       <c r="B1" s="7" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n"/>
-      <c r="B2" s="7" t="n"/>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Claude, on behalf of the team - added in response to Ryo's 8/13 request in #hack-team-12 to start identifying the capabilities the AI tool should have.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Author</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Claude, on behalf of the team - added in response to Ryo's 8/13 request in #hack-team-12 to start identifying the capabilities the AI tool should have.</t>
+          <t>Ryo's Sheet1 columns (Requirement ID / Category / AI Tool Requirement Description) are unchanged, and requirements 1-5 are exactly as he wrote them. New rows continue his numbering from 6. Nothing was renamed, reordered, or overwritten.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Step markers</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Ryo's Sheet1 columns (Requirement ID / Category / AI Tool Requirement Description) are unchanged, and requirements 1-5 are exactly as he wrote them. New rows continue his numbering from 6. Nothing was renamed, reordered, or overwritten.</t>
+          <t>Every added requirement (6-50) opens with a (Step N) marker tying it to the seven-step process on slide 13 of the Novant App Rat playbook, per Ryo's suggestion that we hang AI insertion points off that workflow. Ryo's own rows 1-5 were left untouched, so their step mapping is recorded below instead.</t>
         </is>
       </c>
     </row>
@@ -1202,14 +1360,10 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="7" t="n"/>
-    </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Open items for Bina</t>
+          <t>Coverage against slide 13's seven-step process</t>
         </is>
       </c>
       <c r="B8" s="7" t="n"/>
@@ -1217,84 +1371,196 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Synthetic data scope</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Bina flagged on 8/12 that the Novant data is missing most cost, contract, technical/business risk, and capability fields, and proposed dummy data. Requirements 16, 19, 20, 24, and 10 all depend on that decision. Recommendation: generate synthetic values for cost, contract, risk, and capability against the real Novant application list, so app names and counts stay realistic while the scored fields are complete. This needs a yes before the scoring work starts - it is the biggest single scope dependency on the sheet.</t>
+          <t>'Application Rationalization Seven-Step Process', slide 13 of Novant_App Rat_Playbook_MVP.pptx (Novant Health, Digital Products &amp; Services - marked preliminary and confidential). Read from the slide image Ryo posted in #hack-team-12 on 2026-08-12.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Capability taxonomy</t>
+          <t>Step 1 - Discovery</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Requirement 19 assumes we adopt an existing published health-system business capability model rather than authoring one on build day. Bina to confirm which one, since every redundancy finding depends on it.</t>
+          <t>Identify current applications and stakeholders; document business objectives and pain points. &gt;&gt; Ryo's REQ 1 (partial - document scanning surfaces objectives and pain points). Added: 8, 11, 14, 18.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Disposition model</t>
+          <t>Step 2 - Inventory &amp; gather data</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Ryo's requirement 4 uses invest / consolidate / replace / retire, so that vocabulary is used throughout rather than the TIME model (tolerate / invest / migrate / eliminate). Flagging in case the team prefers TIME for the client-facing deliverable - they map cleanly, it is only naming.</t>
+          <t>Update catalog with metadata and specifications; map technical dependencies and integrations. &gt;&gt; Ryo's REQ 1, 2, 3. Added: 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 20.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="7" t="n"/>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Step 3 - Analyze &amp; map</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Evaluate business value and technical health; map applications to business capabilities. &gt;&gt; Added: 19, 20, 21, 22, 23, 24, 25, 26, 50. (Ryo's REQ 1-5 do not yet cover scoring - this was the largest gap in the original five.)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Reference material NOT read</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Step 4 - Execute rationalization</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Categorize applications; develop consolidation recommendations. &gt;&gt; Ryo's REQ 4. Added: 25, 26, 27, 28, 29, 30, 47, 50.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Novant playbook slide 13</t>
+          <t>Step 5 - Strategy &amp; roadmap</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ryo asked for AI insertion points hung off the slide 13 workflow in 'Novant_App Rat_Playbook_MVP.pptx'. That file could not be downloaded in this session (no Slack file-fetch capability available to this agent), so the lifecycle stages below were built from the standard App Rat lifecycle and the hackathon prompt instead: inventory &amp; discovery, enrichment, scoring, disposition, roadmap &amp; business case. These almost certainly align with slide 13, but the mapping is unverified - worth a 5-minute check against the actual slide, and the row categories can be relabelled to match his workflow step names.</t>
+          <t>Prioritize initiatives and timeline; define metrics and resource requirements. &gt;&gt; Added: 16, 29, 31, 32, 33, 34, 35, 36, 43.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Infotech templates</t>
+          <t>Step 6 - Execute initiatives</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>The four Infotech templates Bina shared (02-Application-Portfolio-Management-Diagnostic-Tool, 04-Rationalize-Your-Application-Portfolio-Tool, 05-Application-TCO-Calculator, 10-Disposition-Prioritization-Tool) were also not downloadable in this session. The scoring dimensions in requirements 21-24 and the TCO components in requirement 20 are standard, but should be cross-checked against those templates for field-level alignment.</t>
+          <t>Implement changes and migrations; track progress and coordinate teams. &gt;&gt; Added: 36, 37, 38, 39, 40. (Nothing in the original five reached this step.)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Screenshot</t>
+          <t>Step 7 - Monitor &amp; optimize</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>The image Ryo posted at 21:23 UTC on 8/12, immediately after mentioning slide 13, was also not retrievable. If that was the slide 13 workflow, pasting its steps as text into the channel would let the categories be aligned exactly.</t>
+          <t>Measure improvements and savings; adjust strategy based on outcomes. &gt;&gt; Added: 41, 42, 43, 44, 45. (Nothing in the original five reached this step either.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Ryo's REQ 5 (upload/link webpage) and added 46, 47, 48, 49 span the whole process rather than sitting on one step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Open decisions for the team</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Step 4 vocabulary</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Slide 13 step 4 says retain / replace / retire (three categories). Ryo's REQ 4 says invest / consolidate / replace / retire (four). These are not the same set and the difference matters: 'invest' implies new spend, while 'retain' implies leave it alone - a real distinction when the mandate is to cut 15%. 'Consolidate' is also the category most of the savings story lives in, so dropping it would weaken the output. RECOMMENDATION: the engine emits Ryo's four categories, and client-facing Novant materials map them to slide 13's three (invest and consolidate -&gt; retain or replace depending on the survivor; retire -&gt; retire). Needs a decision from Ryo and Bina before the disposition logic is built, since it changes the output schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic data scope</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Bina flagged on 8/12 that the Novant data is missing most cost, contract, technical/business risk, and capability fields, and proposed dummy data. Requirements 10, 16, 19, 20, and 24 all depend on that decision. RECOMMENDATION: generate synthetic values for cost, contract, risk, and capability against the real Novant application list, so app names and counts stay realistic while the scored fields are complete. This needs a yes before the scoring work starts - it is the biggest single scope dependency on the sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Capability taxonomy</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Requirement 19 assumes we adopt an existing published health-system business capability model rather than authoring one on build day. Bina to confirm which one, since every redundancy finding depends on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Demo scope</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Steps 6 and 7 (requirements 37-45) describe post-decision capability, which normally implies a real program running over months. Two of them are demoable on Friday without that: 38 (progress tracking) and 41 (realized vs projected savings) both work by feeding the tool two snapshots of the same portfolio. Worth deciding whether to build one of those, because a tool that closes the loop on whether the savings actually landed is a materially stronger pitch than one that stops at the recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Reference material</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Slide 13 - READ and incorporated</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>The seven-step process from slide 13 of Bina's Novant playbook is now the organizing spine of this sheet; every added requirement carries a (Step N) marker and the coverage map above is built from it. Source: the slide-13 image Ryo posted in #hack-team-12 on 2026-08-12, immediately after suggesting we hang AI insertion points off that workflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Infotech templates - NOT read</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>The four Infotech templates Bina shared on 8/12 (02-Application-Portfolio-Management-Diagnostic-Tool, 04-Rationalize-Your-Application-Portfolio-Tool, 05-Application-TCO-Calculator, 10-Disposition-Prioritization-Tool) could not be downloaded in this session. Bina noted they are somewhat dated and recommended verifying their content independently, so treat them as a cross-check rather than a blocker: the scoring dimensions in requirements 21-24 and the TCO components in requirement 20 are industry-standard, but a field-level comparison against those templates would be worth someone's 15 minutes.</t>
         </is>
       </c>
     </row>

--- a/docs/requirements/Application Rationalization Agent Requirements - filled.xlsx
+++ b/docs/requirements/Application Rationalization Agent Requirements - filled.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>(Step 2) Build an application dependency map from interface inventories, integration/middleware configuration, and narrative descriptions in the scanned documents; emit a directed dependency edge list with confidence per edge - directly serving step 2's 'map technical dependencies and integrations', and the prerequisite for testing any later 'retire' recommendation for downstream breakage. [STRETCH] [DATA GAP: no interface or integration inventory in the Novant extract - needs synthetic dependency data]</t>
+          <t>(Step 2) Build an application dependency map from interface inventories, integration/middleware configuration, and narrative descriptions in the scanned documents; emit a directed dependency edge list with confidence per edge - directly serving step 2's 'map technical dependencies and integrations', and the prerequisite for testing any later 'retire' or 'consolidate' recommendation for downstream breakage. A minimum version must ship in the MVP: a per-application has_downstream_dependents boolean plus an enabling / dependent / overlapping flag on each application pair (three letters per cell, no formulas), which is enough for REQ 25 and REQ 29 to refuse a recommendation that would break a dependent system. [MVP for the minimum dependency signal (has_downstream_dependents plus the E/D/O pair flag); STRETCH for the full confidence-weighted edge list] [DATA GAP: no interface or integration inventory in the source data available to the team - needs synthetic dependency data] [Sequencing decision 2026-08-13: promoted to MVP because REQ 25 and REQ 27 are MVP and must not claim breakage safety they cannot check - see the Notes sheet]</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>(Steps 2, 5) Extract commercial terms from contract and order-form PDFs into structured fields: annual contract value, term start and end, renewal and auto-renewal notice windows, license metric (per-user / per-bed / enterprise / consumption), true-up and early-termination clauses - each with a citation to the clause it came from. Emit a renewal calendar showing which decisions carry a real deadline in the next 12 months, which is what drives roadmap sequencing at step 5. [MVP] [DATA GAP: contract data missing from the Novant extract - synthetic contracts needed]</t>
+          <t>(Steps 2, 5) Extract commercial terms from contract and order-form PDFs into structured fields: annual contract value, term start and end, renewal and auto-renewal notice windows, license metric (per-user / per-bed / enterprise / consumption), true-up and early-termination clauses - each with a citation to the clause it came from. Emit a renewal calendar showing which decisions carry a real deadline in the next 12 months, which is what drives roadmap sequencing at step 5. [MVP] [DATA GAP: contract terms missing from the source data available to the team - synthetic contracts needed]</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>(Step 3) Tag every application against a business capability model (for a health system: patient access, revenue cycle, clinical documentation, imaging, pharmacy, supply chain, HR, finance, analytics) with primary and secondary capability tags plus a confidence score, inferred from product documentation and app descriptions - step 3's 'map applications to business capabilities'. This tagging is the foundation for all redundancy detection downstream: if it is wrong, the overlap findings are wrong. [MVP] [DATA GAP: no capability field in the Novant extract] [ASSUMPTION: we adopt an existing published health-system capability taxonomy rather than authoring one on build day - Bina to confirm]</t>
+          <t>(Step 3) Tag every application against a business capability model (for a health system: patient access, revenue cycle, clinical documentation, imaging, pharmacy, supply chain, HR, finance, analytics) with primary and secondary capability tags plus a confidence score, inferred from product documentation and app descriptions - step 3's 'map applications to business capabilities'. This tagging is the foundation for all redundancy detection downstream: if it is wrong, the overlap findings are wrong. [MVP] [DATA GAP: no capability field in the source data available to the team] [ASSUMPTION: we adopt an existing published health-system capability taxonomy rather than authoring one on build day - Bina to confirm]</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>(Steps 2-3) Reconstruct total cost of ownership where source data carries only licence cost: subscription/licence + support and maintenance + infrastructure/hosting + internal FTE support effort, applying documented estimation rules and labelling each component as actual, allocated, or estimated so a CFO can see immediately which figures are defensible and which are modelled. [MVP] [DATA GAP: most cost fields missing from the Novant extract] [Worth cross-checking the component breakdown against Infotech '05-Application-TCO-Calculator.xlsx' that Bina shared - that file was not readable from this session]</t>
+          <t>(Steps 2-3) Reconstruct total cost of ownership from the full component list rather than licence cost alone, enumerating: (1) licence and subscription; (2) external support and maintenance; (3) version-upgrade and additional-module fees; (4) internal labour - development, application support, help desk; (5) infrastructure - storage, server, network, endpoint; (6) indirect costs - formal and informal end-user training, skilled-staff premiums, travel; (7) consumption / usage-based charges (metered, per-request, per-token); plus (8) one-time initial implementation cost, held separately from the recurring run-rate and never netted into it. Label each component actual, allocated, or estimated so a CFO can see immediately which figures are defensible and which are modelled, and publish the estimation rule behind every estimated component (REQ 55). Components 3, 6, 7 and 8 were absent from the original four-component list; omitting them under-counts cost and therefore under-counts savings against the 15% reduction target. [MVP] [DATA GAP: most cost components missing from the source data available to the team - documented estimation rules required]</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>(Step 3) Score business value on a normalized 1-5 scale from weighted sub-factors - criticality to patient care and to revenue, breadth of use (active users vs licences purchased), process centrality, and owner-stated strategic importance - and emit the score together with each sub-factor's contribution, so a stakeholder argues with an input rather than with a black-box number. [MVP]</t>
+          <t>(Step 3) Score business value on a normalized 1-5 scale from weighted sub-factors - criticality to patient care and to revenue, breadth of use (active users vs licences purchased), process centrality, and owner-stated strategic importance - and emit the score together with each sub-factor's contribution, so a stakeholder argues with an input rather than with a black-box number. Every signal feeds exactly one scoring dimension: business value owns criticality, usage breadth, process centrality and owner-stated strategic importance, and consumes no supportability, version-currency, EOL, vendor-viability or risk signal - those belong to REQ 22 and REQ 24 alone. [MVP]</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>(Step 3) Score technical fit and health from supportability (version currency, EOL proximity), architecture fit (integration pattern, cloud readiness, customization debt), operational stability (incident/ticket volume where available), and vendor viability - emitting the score plus the top two drivers pulling it down, which are the inputs to any 'invest' remediation plan. [MVP]</t>
+          <t>(Step 3) Score technical fit and health from supportability (version currency, EOL proximity), architecture fit (integration pattern, cloud readiness, customization debt), operational stability (incident/ticket volume where available), and vendor viability - emitting the score plus the top two drivers pulling it down, which are the inputs to any 'invest' remediation plan. Technical health is the sole owner of version currency, EOL proximity, unsupported-version status and vendor viability; REQ 24 must not re-consume them, because scoring one underlying fact twice fails two of four gates on a single finding and systematically over-recommends retiring old-but-adequate applications. [MVP]</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>(Step 3) Score cost efficiency as TCO against value delivered: cost per active user benchmarked against peer applications in the same capability, and licensed-vs-active seat waste. Report unused-licence spend as its own explicit dollar line item - it is the fastest credible saving available against a 15% reduction target and needs no migration project. [MVP]</t>
+          <t>(Step 3) Score cost efficiency as TCO against value delivered: cost per active user benchmarked against peer applications in the same capability, and licensed-vs-active seat waste. Cost efficiency is the sole owner of the cost signals - cost per active user, unused-licence spend, cost percentile within the capability peer group - and consumes no supportability or risk signal. Report unused-licence spend as its own explicit dollar line item - it is the fastest credible saving available against a 15% reduction target and needs no migration project. [MVP]</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>(Step 3) Score risk on two axes kept deliberately separate rather than blended: technical risk (unsupported versions, single points of failure, no DR/backup, single-vendor concentration) and business/compliance risk (PHI and HIPAA exposure, data residency, SOC 2 / HITRUST posture, vendor financial viability, contractual lock-in). Emit both scores plus the specific findings behind each. [MVP] [DATA GAP: technical and business risk fields missing from the Novant extract - synthetic risk attributes needed]</t>
+          <t>(Step 3) Score risk on axes kept deliberately separate rather than blended: technical risk (single points of failure, no DR/backup, single-vendor concentration, unhardened or unpatched configuration) and business/compliance risk (PHI and HIPAA exposure, data residency, SOC 2 / HITRUST posture, contractual lock-in), plus the clinical / patient-safety axis specified in REQ 65. Emit each score with the specific findings behind it. Risk does not consume unsupported-version status, EOL proximity or vendor financial viability - those are scored once, in REQ 22 - so a single obsolescence fact cannot fail two gates. [MVP] [DATA GAP: technical, compliance and clinical risk attributes missing from the source data available to the team - synthetic risk attributes needed]</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>(Steps 3-4) Detect functional redundancy by grouping applications sharing a business capability tag and comparing feature coverage, user overlap, and cost - emitting ranked overlap clusters with a recommended survivor, the reason it survives, and the consolidation saving available. This is step 4's 'develop consolidation recommendations'. Target output reads like: 'four products cover secure clinical messaging; 2,100 of 3,400 users hold two or more; consolidating to one saves $X annually.' [MVP - this is the demo's money slide]</t>
+          <t>(Steps 3-4) Detect functional redundancy by grouping applications sharing a business capability tag and comparing feature coverage, user overlap, and cost - emitting ranked overlap clusters with a recommended survivor, the reason it survives, and the consolidation saving available. This is step 4's 'develop consolidation recommendations'. Target output reads like: 'four products cover secure clinical messaging; 2,100 of 3,400 users hold two or more; consolidating to one saves $X annually.' Every cluster recommendation is checked against REQ 10's MVP dependency signal before it is published, so a consolidation never claims breakage safety that was not tested. [MVP - this is the demo's money slide]</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>(Step 4) Extend REQ 4: place each application into its disposition category from business value and technical health, with cost, risk, and redundancy as modifiers - and emit for each app a written rationale in consultant language that cites the specific scores and evidence that drove the placement, plus a confidence level. The rationale, not the category, is the deliverable. [MVP] [See the step-4 vocabulary note on the Notes sheet: Ryo's REQ 4 uses invest/consolidate/replace/retire, slide 13 uses retain/replace/retire - needs a team decision]</t>
+          <t>(Step 4) Extend REQ 4: assign every application a disposition from exactly four categories - invest, consolidate, replace, retire - using the pass/fail gate engine specified in REQ 52 rather than a business-value-by-technical-health 2x2 (a 2x2 has no axis on which 'consolidate' can appear, and consolidate is where the savings are). Emit for each application the disposition, its priority, a written rationale in consultant language citing the specific scores, the pass/fail pattern and the evidence that drove the placement, plus a confidence level. The rationale, not the category, is the deliverable. [MVP] [Step 4 vocabulary settled 2026-08-13 by Bina: invest / consolidate / replace / retire, matching the hackathon prompt's own wording. The four terms are emitted directly, with no mapping to any other vocabulary - see the Notes sheet.]</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>(Steps 4-5) Test every 'retire' and 'consolidate' recommendation against the dependency map and the renewal calendar, and defer or downgrade any recommendation that would break a dependent system or trigger an early-termination penalty exceeding the saving. Output these separately as a constrained list with the blocking reason and the date the constraint lifts. [STRETCH]</t>
+          <t>(Steps 4-5) Test every 'retire' and 'consolidate' recommendation against the dependency map, the renewal calendar, and REQ 53's retention expiry, and defer or downgrade any recommendation that would break a dependent system, trigger an early-termination penalty exceeding the saving, or retire an application whose data-retention obligation has not expired. Output these separately as a constrained list with the blocking reason and the date the constraint lifts. [MVP for the minimum check against REQ 10's MVP dependency signal, the renewal calendar and the retention gate; STRETCH for full edge-level deferral scheduling across waves]</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>(Step 5) Quantify savings per recommendation with the arithmetic shown and the assumptions stated (recurring vs one-time, gross vs net of migration cost, realization lag from decision to saved dollar), then roll up to a portfolio figure expressed as a confidence range rather than a single false-precision number. [MVP]</t>
+          <t>(Step 5) Quantify savings per recommendation with the arithmetic shown and the assumptions stated (recurring vs one-time, realization lag from decision to saved dollar), computing net rather than gross saving: current-state TCO, minus the ongoing TCO of the replacement or surviving application, minus amortised one-time migration and implementation cost, minus residual archival and retention cost wherever a REQ 53 data-retention obligation survives retirement. Never assume a retire recommendation returns 100% of an application's cost - in a regulated environment retire is both the disposition most likely to be blocked and the one most likely to leave cost behind. Roll up to a portfolio figure expressed as a confidence range rather than a single false-precision number, reported both as an annual run-rate and as a five-year cumulative per REQ 54. [MVP]</t>
         </is>
       </c>
     </row>
@@ -1271,6 +1271,231 @@
       <c r="C51" s="4" t="inlineStr">
         <is>
           <t>(Steps 3-4) Make the scoring model configurable - weights per scoring dimension and the disposition thresholds - and record which weight set produced a given output, so the same tool can be re-pointed at another client's priorities without re-engineering and prior conclusions stay reproducible. [STRETCH]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Data enrichment</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>(Step 2) Record lifecycle stage (Birth / Growth / Mature / End of Life) and sourcing type (COTS / custom in-house / SaaS / hybrid) for every application, inferred from implementation date, version history, and product metadata where not stated. Both are guardrail fields rather than score inputs: applications in Birth or Growth are excluded from retire and replace outright, and sourcing type gates which dispositions are even legal for an application (a custom application cannot be upgraded to the vendor's current release; a SaaS product cannot be re-platformed). Sourcing type also drives the cost shape in REQ 20 and REQ 55. Without these the engine will recommend retiring a recently implemented application purely because adoption has not ramped yet. Exclusions are applied after the REQ 52 lookup and every suppressed recommendation is recorded with its reason, since a suppressed recommendation with a stated reason is a better artifact than a silently different answer. [MVP] [REF: Infotech 02-Build-an-Application-Rationalization-Framework - lifecycle and application-type criteria with their confirmed/excluded disposition sets; 04-Rationalize-Your-Application-Portfolio-Tool inventory fields]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Application rationalization</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>(Steps 3-4) Implement disposition assignment as an explicit, configurable pass/fail lookup rather than a blended score. Gate each of the four scored dimensions - REQ 21 business value (V), REQ 22 technical health (T), REQ 23 cost efficiency (C), REQ 24 risk (R) - at a per-dimension threshold defaulting to 3.0 on the 1-5 scale, concatenate the four results into a VTCR key such as 'PPFP', and look that key up in an editable 16-row table returning one disposition from invest / consolidate / replace / retire and one priority from Very High / High / Moderate / Low / Very Low. Default table, to be argued with rather than assumed: PPPP invest (Very Low); PPPF invest (High); PPFP invest (Moderate); PPFF invest (High); PFPP invest (Moderate); PFPF invest (High); PFFP replace (High); PFFF replace (Very High); FPPP consolidate (Low); FPPF consolidate (Moderate); FPFP retire (High); FPFF retire (Very High); FFPP consolidate (Moderate); FFPF retire (High); FFFP retire (Very High); FFFF retire (Very High). Thresholds and every table row are configuration, not code. Score each criterion 1-5 in 0.5 increments with an integer weight per criterion where weight 0 disables it, and renormalise each dimension's weighted average over only the criteria that actually carry a value, so an application with sparse data is reported as incomplete by REQ 12 instead of being silently scored downward toward retire. Redundancy is not a gate: cluster membership from REQ 25 is an override that forces consolidate. REQ 51's lifecycle and sourcing exclusions run after the lookup. Store the VTCR key with the recommendation - it is the skeleton of REQ 27's rationale ('passes business value and cost efficiency, fails technical health and risk') - and allow the REQ 30 human override, validated against the same four-term vocabulary. [MVP] [REF: Infotech 04-Rationalize-Your-Application-Portfolio-Tool - weighted per-lens averages, 3.0 pass thresholds, four-character key and 16-row disposition truth table, disposition and priority held as separate fields; its blank-handling defect corrected here]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Data enrichment</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>(Steps 2, 6) Capture data retention and archival obligations as a structured field block per application rather than as prose inside a runbook: compliance requirements, retention policy length, retention expiry date (the date data may actually be deleted), whether the application or its data must remain accessible after retirement and by whom at what access level, archive solution and archival method (cloud / hybrid / on-premise / cold storage), data migration target system, expected access frequency and user count, the classification of information held, the named point person for data extraction, and whether the application can purge data itself. Retention expiry, not contract end date, determines whether an application can be retired now or must first be moved to a read-only archive - so this block gates the retire disposition in REQ 29 and supplies the residual cost that REQ 32 and REQ 54 must subtract. [MVP for the fields and the retirement gate; STRETCH for full archival cost modelling] [REF: standard records-retention practice; no equivalent field block exists anywhere in the Infotech reference set, which treats retirement as cost-free]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Roadmap &amp; sequencing</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>(Step 5) Show the savings arithmetic in full and net out every residual cost: realised saving equals current-state TCO, minus the ongoing TCO of the replacement or surviving application, minus amortised one-time migration and implementation cost, minus archival and retention cost where a REQ 53 obligation persists past retirement. Report every figure both as an annual run-rate and as a five-year cumulative, each labelled, since the CIO's 15% target is a run-rate figure while the reference cost model is a five-year one and conflating them is how a savings number gets challenged and lost. Leave figures undiscounted, matching the reference convention, and state that choice in the output rather than quietly adding NPV. This supersedes the gross-of-residual-cost arithmetic in the original REQ 32, which has been updated in place to match. [MVP] [REF: Infotech 05-Application-TCO-Calculator - five-year horizon, side-by-side option blocks for costing the alternative, and its explicit exclusion of depreciation and time value of money]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Data enrichment</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>(Steps 2-3) Publish and apply the estimation rule behind every modelled component of REQ 20's eight-part cost model, so a CFO can challenge the rule rather than the number: internal support labour derived from user count and sourcing type (baseline circa 0.25 FTE per COTS/SaaS application and circa 1.0 FTE per custom application, scaled by user band and multiplied by a loaded FTE rate); version-upgrade and additional-module fees as a percentage of licence for on-premise COTS and zero for SaaS where they are bundled; indirect and training cost as a year-one percentage of licence plus an annual churn allowance; infrastructure allocated only for on-premise and hosted applications and driven off the REQ 57 footprint rather than a flat percentage. Consumption / usage-based pricing has no equivalent in the reference cost model and must be modelled from first principles, since it is the dominant cost structure for SaaS renewals and the primary one for the AI tools in REQ 11. Every component stays labelled actual, allocated, or estimated per REQ 20. [MVP] [REF: Infotech 05-Application-TCO-Calculator - its five cost categories and their line items; 02-Build-an-Application-Rationalization-Framework adds one-time initial cost and the cost-intensity-by-application-type table; the consumption component is ours, the reference model has no line for it]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Roadmap &amp; sequencing</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>(Step 5) Decompose the effort and urgency inputs that REQ 31 and REQ 33 currently treat as single bands. Score technical complexity as a weighted roll-up of impacted integrations (weight 4), impacted code (4), data migration or transformation (3), and overall complexity (2), each rated High / Medium / Low / None. Score urgency as the average of timeline sensitivity and severity of risk or pain point on the same rating vocabulary. Normalise both to 0-1 over the sum of the weights - not over the count of weights, which is the arithmetic defect in the reference tool and makes its 'weighted average' incomparable across weight configurations - and define explicit numeric wave cutoffs rather than reading priority off a bubble chart by eye: wave 1 where urgency is at or above 0.75, or effort is in the bottom third against a material net saving; wave 3 where complexity is in the top third or a dependency, retention or contract constraint blocks it; wave 2 for the remainder, sorted within wave by net saving divided by effort. [MVP for the complexity and urgency scores; STRETCH for fully automated wave assignment] [REF: Infotech 10-Disposition-Prioritization-Tool - its three scoring axes, default attribute weights and High/Medium/Low/No rating maps; the cutoffs and the normalisation fix are ours, the source tool has no numeric priority formula at all]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Data collection</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>(Step 2) Capture the infrastructure and data footprint of each application alongside the application-to-application dependency edges in REQ 10: server names, database server and database name, database type, data size, hosting environment, and the type of data held (database, images, documents). This is what makes the infrastructure component of REQ 20 computable, what sizes the archival obligation in REQ 53, and what lets REQ 37's decommission runbook name the specific servers and databases to be reclaimed - which is where a large share of both the real decommission effort and the realisable infrastructure saving sits. [MVP for the fields; STRETCH for automated reclamation costing] [REF: Infotech 04-Rationalize-Your-Application-Portfolio-Tool - hardware dependencies held separately from software dependencies]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Data enrichment</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>(Steps 4-6) Record the named replacement or successor application for every consolidate and replace disposition, together with its planned go-live date and its own ongoing TCO. REQ 39 promises to detect 'a retirement scheduled before its replacement goes live' and REQ 32 and REQ 54 require netting the replacement's ongoing cost out of the saving; neither is computable while the replacement exists only as prose inside a rationale. This field is the join that makes the wave sequencing in REQ 31 and the conflict detection in REQ 39 work. [MVP] [REF: internal - required by REQ 32, REQ 39 and REQ 54]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Data enrichment</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>(Steps 1-3) Tag every application on an organizational dimension kept deliberately separate from the business-capability tags in REQ 19: legal entity, business unit, department, business function or workstream, cost centre, and program. Capability answers what an application does; the organizational dimension answers whose budget carries it and whose share of the 15% a given saving lands in. Every portfolio figure - spend, application count, redundancy, savings - must be sliceable on both dimensions independently, and for a 600-application portfolio the organizational axis is how a CIO allocates the target. [MVP] [REF: Infotech 04-Rationalize-Your-Application-Portfolio-Tool - Snapshot Groupings 1-3 (business units, departments, functions, value streams, markets) held deliberately separate from business capability]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Application rationalization</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>(Steps 3-4) Detect merger- and acquisition-driven duplication as a named redundancy pattern: where two applications covering the same business capability originate from different legal entities, pair them explicitly and recommend a survivor on value, cost, user count and contract runway rather than on which entity acquired the other. Post-merger duplicate stacks are the largest and most predictable source of consolidation saving in an organization that has grown by acquisition, and they are partly invisible to capability-only overlap detection because each application is sanctioned within its own entity. [MVP] [REF: Infotech 02-Application-Portfolio-Management-Diagnostic-Tool - mergers and acquisitions named as one of four application-sprawl drivers]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Data analysis</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>(Step 2) Extend REQ 8 to run the source reconciliation in both directions and store the result as per-application presence flags with a reconciliation date: found in the CMDB, found in the contract register, found in finance or AP, seen in SSO sign-in activity. REQ 8 already surfaces spend or usage with no governance record. The reciprocal exception - a governed, catalogued application whose contract or cost cannot be located - is at least as common in practice and blocks any credible savings claim on that application, so raise it as its own work item naming the specific missing source. [MVP] [REF: internal - the reciprocal direction of the same join REQ 8 already performs; no Infotech template covers it]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Data analysis</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>(Step 3) Roll the per-application scores up to a business-capability view: for each capability, average the dimension scores of every application mapped to it, apply configurable per-dimension weightings that must total 100%, and band the result as Strong (above 75%), Improve (50-75%), Remediate (25-50%) or Critical Need (0-25%). Report capability coverage alongside capability spend and application count, so the portfolio can be read as 'where are we over-invested and under-served' rather than only as a list of per-application verdicts. This is a second analysis mode distinct from per-application disposition, and it is the natural executive view. [MVP for the rollup and the bands; STRETCH for configurable weightings] [REF: Infotech 04-Rationalize-Your-Application-Portfolio-Tool - Group 1/2/3 Results, its capability weighting rows and its four performance bands]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Data analysis</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>(Steps 2-3) Classify every application on a governance-visibility axis - Managed (under IT oversight with a named owner and a contract), Unmanaged (known but with no owner or no contract), Unknown (evidenced only by spend or sign-in activity), Unsanctioned (in use against policy) - and report the portfolio split with the annual spend sitting behind each category. This turns REQ 8's shadow-IT findings and REQ 61's reconciliation flags into a single portfolio-level figure, and unmanaged plus unknown spend is normally the fastest defensible block of a 15% reduction. [MVP] [REF: Infotech 02-Application-Portfolio-Management-Diagnostic-Tool - the Managed / Unmanaged / Unknown / Unsanctioned visibility taxonomy and its IT-oversight definitions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Execution &amp; tracking</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>(Steps 4-6) Separate recommendation from execution state as three distinct fields rather than overloading one: disposition (invest / consolidate / replace / retire), action (the specific verb - re-platform, upgrade, remediate, retrain, merge, absorb, decommission, modernize), and workflow status drawn from a controlled, configurable execution-stage vocabulary covering contract termination, compliance and archival review, application retirement, and per-team infrastructure decommission closure steps. Disposition answers what we recommend, action answers what will be done, status answers how far it has got - and status is what REQ 38's progress tracking reports against. [MVP for the three-field split and a first-pass status enum; STRETCH for the full multi-team execution pipeline] [REF: Infotech 04-Rationalize-Your-Application-Portfolio-Tool and 10-Disposition-Prioritization-Tool - both hold disposition and priority as separate fields; execution status has no equivalent in either and is defined by us]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Data analysis</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>(Step 3) Add clinical and patient-safety risk as a third risk axis in REQ 24, kept separate from technical risk and from business/compliance risk: direct involvement in patient care delivery, clinical documentation or medication workflows, and the patient-safety consequence of unavailability. In a health system this is neither a compliance question nor a technical one, and collapsing it into either produces recommendations a clinical stakeholder will reject on sight. Clinical risk is scored from signals owned by no other dimension, and any application scoring high on it is excluded from wave 1 regardless of the saving available. [MVP] [REF: health-system domain requirement; no Infotech template carries a clinical or patient-safety axis]</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1320,7 +1545,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Ryo's Sheet1 columns (Requirement ID / Category / AI Tool Requirement Description) are unchanged, and requirements 1-5 are exactly as he wrote them. New rows continue his numbering from 6. Nothing was renamed, reordered, or overwritten.</t>
+          <t>Ryo's Sheet1 columns (Requirement ID / Category / AI Tool Requirement Description) are unchanged, and requirements 1-5 are exactly as he wrote them. New rows continue his numbering from 6, now running to 65. Nothing was renamed, reordered, or overwritten; where an existing added requirement needed correcting (10, 16, 19, 20, 21, 22, 23, 24, 25, 27, 29, 32) it was edited in place and the change is recorded below.</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1557,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Every added requirement (6-50) opens with a (Step N) marker tying it to the seven-step process on slide 13 of the Novant App Rat playbook, per Ryo's suggestion that we hang AI insertion points off that workflow. Ryo's own rows 1-5 were left untouched, so their step mapping is recorded below instead.</t>
+          <t>Every added requirement (6-65) opens with a (Step N) marker tying it to the seven-step process on slide 13 of the Novant App Rat playbook, per Ryo's suggestion that we hang AI insertion points off that workflow. Ryo's own rows 1-5 were left untouched, so their step mapping is recorded below instead.</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1581,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>[MVP] = should be demonstrable on Friday. [STRETCH] = designed for, built only if time allows. [DATA GAP: ...] = depends on data the team does not currently have. [ASSUMPTION: ...] = a call made without confirmation, please review.</t>
+          <t>[MVP] = should be demonstrable on Friday. [STRETCH] = designed for, built only if time allows. [DATA GAP: ...] = depends on data the team does not currently have. [ASSUMPTION: ...] = a call made without confirmation, please review. [REF: ...] = on requirements 51-65 only, the reference framework the requirement is traceable to, so provenance survives a copy-paste.</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1613,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Identify current applications and stakeholders; document business objectives and pain points. &gt;&gt; Ryo's REQ 1 (partial - document scanning surfaces objectives and pain points). Added: 8, 11, 14, 18.</t>
+          <t>Identify current applications and stakeholders; document business objectives and pain points. &gt;&gt; Ryo's REQ 1 (partial - document scanning surfaces objectives and pain points). Added: 8, 11, 14, 18, 59.</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1625,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Update catalog with metadata and specifications; map technical dependencies and integrations. &gt;&gt; Ryo's REQ 1, 2, 3. Added: 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 20.</t>
+          <t>Update catalog with metadata and specifications; map technical dependencies and integrations. &gt;&gt; Ryo's REQ 1, 2, 3. Added: 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 20, 51, 53, 55, 57, 59, 61, 63.</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1637,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Evaluate business value and technical health; map applications to business capabilities. &gt;&gt; Added: 19, 20, 21, 22, 23, 24, 25, 26, 50. (Ryo's REQ 1-5 do not yet cover scoring - this was the largest gap in the original five.)</t>
+          <t>Evaluate business value and technical health; map applications to business capabilities. &gt;&gt; Added: 19, 20, 21, 22, 23, 24, 25, 26, 50, 52, 55, 59, 60, 62, 63, 65. (Ryo's REQ 1-5 do not yet cover scoring - this was the largest gap in the original five.)</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1649,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Categorize applications; develop consolidation recommendations. &gt;&gt; Ryo's REQ 4. Added: 25, 26, 27, 28, 29, 30, 47, 50.</t>
+          <t>Categorize applications; develop consolidation recommendations. &gt;&gt; Ryo's REQ 4. Added: 25, 26, 27, 28, 29, 30, 47, 50, 52, 58, 60, 64.</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1661,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Prioritize initiatives and timeline; define metrics and resource requirements. &gt;&gt; Added: 16, 29, 31, 32, 33, 34, 35, 36, 43.</t>
+          <t>Prioritize initiatives and timeline; define metrics and resource requirements. &gt;&gt; Added: 16, 29, 31, 32, 33, 34, 35, 36, 43, 54, 56.</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1673,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Implement changes and migrations; track progress and coordinate teams. &gt;&gt; Added: 36, 37, 38, 39, 40. (Nothing in the original five reached this step.)</t>
+          <t>Implement changes and migrations; track progress and coordinate teams. &gt;&gt; Added: 36, 37, 38, 39, 40, 53, 58, 64. (Nothing in the original five reached this step.)</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1704,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Open decisions for the team</t>
+          <t>Decisions made and open questions</t>
         </is>
       </c>
       <c r="B19" s="7" t="n"/>
@@ -1487,12 +1712,12 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Step 4 vocabulary</t>
+          <t>Step 4 vocabulary - DECIDED 2026-08-13</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Slide 13 step 4 says retain / replace / retire (three categories). Ryo's REQ 4 says invest / consolidate / replace / retire (four). These are not the same set and the difference matters: 'invest' implies new spend, while 'retain' implies leave it alone - a real distinction when the mandate is to cut 15%. 'Consolidate' is also the category most of the savings story lives in, so dropping it would weaken the output. RECOMMENDATION: the engine emits Ryo's four categories, and client-facing Novant materials map them to slide 13's three (invest and consolidate -&gt; retain or replace depending on the survivor; retire -&gt; retire). Needs a decision from Ryo and Bina before the disposition logic is built, since it changes the output schema.</t>
+          <t>DECIDED by Bina on 2026-08-13 at 4:23pm ET: the disposition vocabulary is exactly four terms - invest, consolidate, replace, retire - chosen to match the wording of the hackathon prompt itself, which is also what Ryo's REQ 4 already said. The engine emits those four directly. There is no mapping layer to slide 13's retain / replace / retire and no five-category variant with a separate 'retain'; the earlier recommendation to map down to slide 13's three terms is withdrawn. One supporting observation worth keeping: every Info-Tech tool we reviewed keeps a consolidate-equivalent (Consolidate, Merge, Absorb, Refocus) while slide 13 does not, which supports the choice - consolidation is where the savings story lives (REQ 25). One consequence to build to: with no separate 'retain' term, 'invest' covers both a healthy application kept as it is and one carrying a funded remediation; the two are distinguished by the REQ 52 pass/fail pattern and priority, which are stored with every disposition. Requirements carrying this decision: 4 (Ryo's, already consistent), 27, 52, 64.</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1729,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Bina flagged on 8/12 that the Novant data is missing most cost, contract, technical/business risk, and capability fields, and proposed dummy data. Requirements 10, 16, 19, 20, and 24 all depend on that decision. RECOMMENDATION: generate synthetic values for cost, contract, risk, and capability against the real Novant application list, so app names and counts stay realistic while the scored fields are complete. This needs a yes before the scoring work starts - it is the biggest single scope dependency on the sheet.</t>
+          <t>The overarching prompt describes a 600-application portfolio, so the demo runs on a synthetic portfolio generated to that scale. No client operational data is ingested, used, or committed (see 'Client data - out of scope' below). What must be synthesized, by field category: business-capability tags (REQ 19); active-usage telemetry as distinct from purchased entitlements (REQ 21, 23); most of the per-component TCO breakdown (REQ 20, 55); risk attributes, technical, compliance and clinical (REQ 24, 65); dependency edges and the infrastructure/data footprint (REQ 10, 57); lifecycle stage and sourcing type (REQ 51); retention and archival obligations (REQ 53); and contract terms beyond identifier and end date (REQ 16). Generation rules must be published alongside the data so nothing modelled can be mistaken for measured (REQ 49). Still needs a yes on scale and generation approach before the scoring work starts - it remains the biggest single scope dependency on the sheet.</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1780,84 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Infotech templates - NOT read</t>
+          <t>Infotech templates - READ 2026-08-13</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>The four Infotech templates Bina shared on 8/12 (02-Application-Portfolio-Management-Diagnostic-Tool, 04-Rationalize-Your-Application-Portfolio-Tool, 05-Application-TCO-Calculator, 10-Disposition-Prioritization-Tool) could not be downloaded in this session. Bina noted they are somewhat dated and recommended verifying their content independently, so treat them as a cross-check rather than a blocker: the scoring dimensions in requirements 21-24 and the TCO components in requirement 20 are industry-standard, but a field-level comparison against those templates would be worth someone's 15 minutes.</t>
+          <t>All five Info-Tech references Bina shared were read in full on 2026-08-13 (02-Application-Portfolio-Management-Diagnostic-Tool, 02-Build-an-Application-Rationalization-Framework, 04-Rationalize-Your-Application-Portfolio-Tool, 05-Application-TCO-Calculator, 10-Disposition-Prioritization-Tool), which replaces the earlier 'not read' caveat on this row. What they validated: the scoring dimensions behind REQ 21-24 (weighted multi-lens scoring, gates, then disposition plus priority, is still current practice and matches what Gartner TIME, LeanIX, Apptio and ServiceNow APM do today); the TCO component taxonomy now enumerated in REQ 20 and REQ 55; the prioritisation axes in REQ 56; and the disposition mechanism now specified in REQ 52, which is borrowed from the portfolio tool rather than invented. Two genuine obsolescence findings, both of which we have to fix rather than copy: (1) there is no line item anywhere in the reference cost model for consumption or usage-based pricing, which is now the dominant SaaS metric and the primary cost model for the AI tools the prompt calls out - REQ 20 and REQ 55 add it with no precedent to borrow; (2) every scoring input in every template assumes a human fills in a 1-5 grid in a facilitated workshop, which is precisely the step this agent removes - the methodology is current, its data acquisition is a decade behind, and that gap is the pitch (REQ 6-8 derive usage, spend and shadow IT from SSO, AP and contract data instead of asking people). Build caution: the files are internally inconsistent in places - duplicated and misspelled subtotal labels, dropdown lists feeding columns they no longer match, named ranges resolving to #REF!, and one disposition category defined but unreachable from its own lookup table - so nothing was ported without checking it against the file's own cached values, and anything not already written into these requirements should be re-derived rather than copied. Scale note: those tools cap at roughly 500, 25 and 12 records respectively, so they are unusable as tools at 600 applications - only their logic ports. They are licensed third-party vendor material and this repo is public: cite them, never reproduce or commit them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>AI requirements - no external validation</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>None of the reference material mentions AI at all - zero occurrences across all five Info-Tech templates and slide 13's seven-step process. REQ 11 (AI tools and agents as a first-class inventory category), REQ 26 (a capability bought standalone that is already entitled inside an existing enterprise licence) and the consumption-pricing component in REQ 20 and REQ 55 therefore have no external cross-check available: no precedent, no field taxonomy, no scoring rubric. That makes them simultaneously the clearest differentiator on this sheet and the part with the least outside validation, so they need the most internal scrutiny before Friday - someone other than the author should review those requirements specifically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Dependency guardrail - DECIDED</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>The sheet previously tagged REQ 10 (dependency map) and REQ 29 (breakage and renewal test) STRETCH while REQ 25 (consolidation recommendations) and REQ 27 (disposition assignment) were MVP - so as specified, the Friday tool would recommend retirements and consolidations with no breakage check at all. Of the two available fixes, promote the guardrail or scope consolidation MVP to explicitly disclaim breakage safety, we chose to PROMOTE. REQ 10 now ships an MVP minimum: a per-application has_downstream_dependents boolean plus an enabling / dependent / overlapping flag on each application pair, which is three letters per cell and no formulas. REQ 29's minimum check against that signal, the renewal calendar and REQ 53's retention expiry is MVP too, and REQ 25 now states that every cluster recommendation is checked before it is published. The full confidence-weighted edge list and edge-level deferral scheduling stay STRETCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Cost and savings model - corrected</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Two arithmetic corrections, both of which move the headline number. (1) REQ 20's component list went from four components to eight: licence and subscription; external support and maintenance; version-upgrade and additional-module fees; internal labour; infrastructure; indirect and training costs; consumption / usage-based charges; and one-time implementation cost held separately from the recurring run-rate. Upgrade and module fees, indirect and training cost, and one-time implementation were all missing, and under-counted cost under-counts savings against the 15% target. REQ 55 carries the published estimation rule for every modelled component. (2) REQ 32 now computes net rather than gross saving - current TCO, minus the replacement or survivor's ongoing TCO, minus amortised one-time migration and implementation cost, minus residual archival and retention cost where a REQ 53 obligation outlives the application - and REQ 54 requires every figure reported both as an annual run-rate and as an undiscounted five-year cumulative. A retire recommendation does not return 100% of an application's cost; in a regulated environment retire is both the disposition most likely to be blocked and the one most likely to leave residual cost behind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Scoring input partition</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Business value (REQ 21), technical health (REQ 22), cost efficiency (REQ 23) and risk (REQ 24) previously shared inputs: unsupported versions and vendor viability were scored in both technical health and risk, so one obsolescence fact failed two of the four gates and the engine systematically over-recommended retiring old-but-adequate applications. Every signal now belongs to exactly one dimension, stated in the text of each requirement so the partition survives into the build. REQ 22 owns version currency, EOL proximity, unsupported-version status, architecture fit, operational stability and vendor viability. REQ 24 owns single points of failure, absent DR or backup, single-vendor concentration, unhardened configuration, PHI and HIPAA exposure, data residency, SOC 2 / HITRUST posture and contractual lock-in. REQ 65 owns the clinical and patient-safety axis. REQ 23 owns the cost signals. REQ 21 owns criticality, usage breadth, process centrality and owner-stated strategic importance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Disposition engine - specified</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>REQ 52 pins the mechanism the sheet previously left open, concretely enough to code: gate REQ 21, 22, 23 and 24 at 3.0 on the 1-5 scale, concatenate the four pass/fail results into a VTCR key, look that key up in a 16-row editable table returning one of the four agreed dispositions plus a priority (Very High through Very Low), store the key as the human-readable rationale skeleton REQ 27 needs, force consolidate wherever REQ 25 finds cluster membership, apply REQ 51's lifecycle and sourcing exclusions after the lookup and record every suppression with its reason, and allow the REQ 30 human override validated against the same four terms. The default 16-row mapping is written into REQ 52 and is configuration rather than code, which means a client can argue with the table directly instead of with a black box. Note also that the value-by-health 2x2 in REQ 4 and REQ 27 remains the right chart but cannot be the engine: a 2x2 has no axis on which 'consolidate' can appear, and consolidate is where the savings are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Client data - out of scope</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Bina ruled client operational data out of scope on 2026-08-13. Nothing in this workbook derives from it: no application inventory, no named individuals, no contract identifiers, no cost or contract actuals, no server names, and no departments or legal entities appear anywhere in these requirements, and none may be added. This repository is public, which means there is no access-control boundary of any kind and git history is permanent, so the same standard applies to every file committed here - generic methodology and field names are in scope, client content is not. The demo runs on the synthetic portfolio described above.</t>
         </is>
       </c>
     </row>

--- a/docs/requirements/Application Rationalization Agent Requirements - filled.xlsx
+++ b/docs/requirements/Application Rationalization Agent Requirements - filled.xlsx
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>'Application Rationalization Seven-Step Process', slide 13 of Novant_App Rat_Playbook_MVP.pptx (Novant Health, Digital Products &amp; Services - marked preliminary and confidential). Read from the slide image Ryo posted in #hack-team-12 on 2026-08-12.</t>
+          <t>'Application Rationalization Seven-Step Process', slide 13 of Novant_App Rat_Playbook_MVP.pptx (Novant Health, Digital Products &amp; Services). This seven-step process is the framework the requirements below are built against. Read from the slide image Ryo posted in #hack-team-12 on 2026-08-12.</t>
         </is>
       </c>
     </row>

--- a/docs/requirements/Application Rationalization Agent Requirements - filled.xlsx
+++ b/docs/requirements/Application Rationalization Agent Requirements - filled.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overarching Prompt" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; assumptions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Overarching Prompt" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Notes &amp; assumptions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -580,7 +580,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Analyze collected data and categorize applications into four separate categories (invest, consolidate, replace, or retire) based on critical data points.</t>
+          <t>Analyze collected data and categorize applications into five separate categories (retain, invest, consolidate, replace, or retire) based on critical data points.</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>(Step 4) Extend REQ 4: assign every application a disposition from exactly four categories - invest, consolidate, replace, retire - using the pass/fail gate engine specified in REQ 52 rather than a business-value-by-technical-health 2x2 (a 2x2 has no axis on which 'consolidate' can appear, and consolidate is where the savings are). Emit for each application the disposition, its priority, a written rationale in consultant language citing the specific scores, the pass/fail pattern and the evidence that drove the placement, plus a confidence level. The rationale, not the category, is the deliverable. [MVP] [Step 4 vocabulary settled 2026-08-13 by Bina: invest / consolidate / replace / retire, matching the hackathon prompt's own wording. The four terms are emitted directly, with no mapping to any other vocabulary - see the Notes sheet.]</t>
+          <t>(Step 4) Extend REQ 4: assign every application a disposition from exactly five categories - retain, invest, consolidate, replace, retire - using the pass/fail gate engine specified in REQ 52 rather than a business-value-by-technical-health 2x2 (a 2x2 has no axis on which 'consolidate' can appear, and consolidate is where the savings are). Emit for each application the disposition, its priority, a written rationale in consultant language citing the specific scores, the pass/fail pattern and the evidence that drove the placement, plus a confidence level. The rationale, not the category, is the deliverable. [MVP] [Step 4 vocabulary settled 2026-08-14 by Bina: retain / invest / consolidate / replace / retire. The five terms are emitted directly, with no mapping to any other vocabulary. Retain and invest are separate dispositions rather than one term read at two priorities: retain is a healthy application left alone with no new spend, invest is a funded remediation or enhancement - a deliberate injection of money or effort. This supersedes the four-term position of 2026-08-13, under which 'invest' carried both senses and only its priority told them apart - see the Notes sheet.]</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>(Steps 3-4) Implement disposition assignment as an explicit, configurable pass/fail lookup rather than a blended score. Gate each of the four scored dimensions - REQ 21 business value (V), REQ 22 technical health (T), REQ 23 cost efficiency (C), REQ 24 risk (R) - at a per-dimension threshold defaulting to 3.0 on the 1-5 scale, concatenate the four results into a VTCR key such as 'PPFP', and look that key up in an editable 16-row table returning one disposition from invest / consolidate / replace / retire and one priority from Very High / High / Moderate / Low / Very Low. Default table, to be argued with rather than assumed: PPPP invest (Very Low); PPPF invest (High); PPFP invest (Moderate); PPFF invest (High); PFPP invest (Moderate); PFPF invest (High); PFFP replace (High); PFFF replace (Very High); FPPP consolidate (Low); FPPF consolidate (Moderate); FPFP retire (High); FPFF retire (Very High); FFPP consolidate (Moderate); FFPF retire (High); FFFP retire (Very High); FFFF retire (Very High). Thresholds and every table row are configuration, not code. Score each criterion 1-5 in 0.5 increments with an integer weight per criterion where weight 0 disables it, and renormalise each dimension's weighted average over only the criteria that actually carry a value, so an application with sparse data is reported as incomplete by REQ 12 instead of being silently scored downward toward retire. Redundancy is not a gate: cluster membership from REQ 25 is an override that forces consolidate. REQ 51's lifecycle and sourcing exclusions run after the lookup. Store the VTCR key with the recommendation - it is the skeleton of REQ 27's rationale ('passes business value and cost efficiency, fails technical health and risk') - and allow the REQ 30 human override, validated against the same four-term vocabulary. [MVP] [REF: Infotech 04-Rationalize-Your-Application-Portfolio-Tool - weighted per-lens averages, 3.0 pass thresholds, four-character key and 16-row disposition truth table, disposition and priority held as separate fields; its blank-handling defect corrected here]</t>
+          <t>(Steps 3-4) Implement disposition assignment as an explicit, configurable pass/fail lookup rather than a blended score. Gate each of the four scored dimensions - REQ 21 business value (V), REQ 22 technical health (T), REQ 23 cost efficiency (C), REQ 24 risk (R) - at a per-dimension threshold defaulting to 3.0 on the 1-5 scale, concatenate the four results into a VTCR key such as 'PPFP', and look that key up in an editable 16-row table returning one disposition from retain / invest / consolidate / replace / retire and one priority from Very High / High / Moderate / Low / Very Low. Default table, to be argued with rather than assumed: PPPP retain (Very Low); PPPF invest (High); PPFP invest (Moderate); PPFF invest (High); PFPP invest (Moderate); PFPF invest (High); PFFP replace (High); PFFF replace (Very High); FPPP consolidate (Low); FPPF consolidate (Moderate); FPFP retire (High); FPFF retire (Very High); FFPP consolidate (Moderate); FFPF retire (High); FFFP retire (Very High); FFFF retire (Very High). The all-pass key PPPP is the only retain row, and it is what separates retain from invest: an application that clears every gate is healthy and needs no new spend, while every invest row fails at least one gate, so an invest recommendation always names the specific dimension the money is being spent on. Before 2026-08-14 PPPP returned invest at Very Low priority and those two cases were distinguished by priority alone; they are now distinct dispositions and priority is left to do only its own job. A failure of cost efficiency alone (PPFP) resolves to invest, never to retire. Thresholds and every table row are configuration, not code. Score each criterion 1-5 in 0.5 increments with an integer weight per criterion where weight 0 disables it, and renormalise each dimension's weighted average over only the criteria that actually carry a value, so an application with sparse data is reported as incomplete by REQ 12 instead of being silently scored downward toward retire. Redundancy is not a gate: cluster membership from REQ 25 is an override that forces consolidate. REQ 51's lifecycle and sourcing exclusions run after the lookup. Store the VTCR key with the recommendation - it is the skeleton of REQ 27's rationale ('passes business value and cost efficiency, fails technical health and risk') - and allow the REQ 30 human override, validated against the same five-term vocabulary. [MVP] [REF: Infotech 04-Rationalize-Your-Application-Portfolio-Tool - weighted per-lens averages, 3.0 pass thresholds, four-character key and 16-row disposition truth table, disposition and priority held as separate fields; its blank-handling defect corrected here]</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>(Steps 4-6) Separate recommendation from execution state as three distinct fields rather than overloading one: disposition (invest / consolidate / replace / retire), action (the specific verb - re-platform, upgrade, remediate, retrain, merge, absorb, decommission, modernize), and workflow status drawn from a controlled, configurable execution-stage vocabulary covering contract termination, compliance and archival review, application retirement, and per-team infrastructure decommission closure steps. Disposition answers what we recommend, action answers what will be done, status answers how far it has got - and status is what REQ 38's progress tracking reports against. [MVP for the three-field split and a first-pass status enum; STRETCH for the full multi-team execution pipeline] [REF: Infotech 04-Rationalize-Your-Application-Portfolio-Tool and 10-Disposition-Prioritization-Tool - both hold disposition and priority as separate fields; execution status has no equivalent in either and is defined by us]</t>
+          <t>(Steps 4-6) Separate recommendation from execution state as three distinct fields rather than overloading one: disposition (retain / invest / consolidate / replace / retire), action (the specific verb - monitor, re-platform, upgrade, remediate, retrain, merge, absorb, decommission, modernize), and workflow status drawn from a controlled, configurable execution-stage vocabulary covering contract termination, compliance and archival review, application retirement, and per-team infrastructure decommission closure steps. Disposition answers what we recommend, action answers what will be done, status answers how far it has got - and status is what REQ 38's progress tracking reports against. [MVP for the three-field split and a first-pass status enum; STRETCH for the full multi-team execution pipeline] [REF: Infotech 04-Rationalize-Your-Application-Portfolio-Tool and 10-Disposition-Prioritization-Tool - both hold disposition and priority as separate fields; execution status has no equivalent in either and is defined by us]</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Ryo's Sheet1 columns (Requirement ID / Category / AI Tool Requirement Description) are unchanged, and requirements 1-5 are exactly as he wrote them. New rows continue his numbering from 6, now running to 65. Nothing was renamed, reordered, or overwritten; where an existing added requirement needed correcting (10, 16, 19, 20, 21, 22, 23, 24, 25, 27, 29, 32) it was edited in place and the change is recorded below.</t>
+          <t>Ryo's Sheet1 columns (Requirement ID / Category / AI Tool Requirement Description) are unchanged, and requirements 1-5 are exactly as he wrote them apart from REQ 4, where the five-term disposition vocabulary decided on 2026-08-14 was corrected in place (vocabulary only, no change of meaning) - the single edit to his rows. New rows continue his numbering from 6, now running to 65. Nothing was renamed, reordered, or overwritten; where an existing added requirement needed correcting (10, 16, 19, 20, 21, 22, 23, 24, 25, 27, 29, 32) it was edited in place and the change is recorded below. The 2026-08-14 vocabulary change edited 4, 27, 52 and 64 in place; the requirement count stays at 65 and nothing was split.</t>
         </is>
       </c>
     </row>
@@ -1585,6 +1585,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
@@ -1701,6 +1702,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -1712,150 +1714,199 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Step 4 vocabulary - DECIDED 2026-08-13</t>
+          <t>Step 4 vocabulary - DECIDED 2026-08-14 (supersedes 2026-08-13)</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>DECIDED by Bina on 2026-08-13 at 4:23pm ET: the disposition vocabulary is exactly four terms - invest, consolidate, replace, retire - chosen to match the wording of the hackathon prompt itself, which is also what Ryo's REQ 4 already said. The engine emits those four directly. There is no mapping layer to slide 13's retain / replace / retire and no five-category variant with a separate 'retain'; the earlier recommendation to map down to slide 13's three terms is withdrawn. One supporting observation worth keeping: every Info-Tech tool we reviewed keeps a consolidate-equivalent (Consolidate, Merge, Absorb, Refocus) while slide 13 does not, which supports the choice - consolidation is where the savings story lives (REQ 25). One consequence to build to: with no separate 'retain' term, 'invest' covers both a healthy application kept as it is and one carrying a funded remediation; the two are distinguished by the REQ 52 pass/fail pattern and priority, which are stored with every disposition. Requirements carrying this decision: 4 (Ryo's, already consistent), 27, 52, 64.</t>
+          <t>DECIDED by Bina Din on 2026-08-14: the disposition vocabulary is five terms - retain, invest, consolidate, replace, retire. Asked to confirm that the four-term version read correctly in front of a steering committee, her answer was: 'No, separate by invest, retain, consolidate, replace, and retire.' Definitions, to be used exactly as written in every output: RETAIN - healthy, leave alone, no new spend. INVEST - fund a remediation or enhancement; a deliberate injection of money or effort. CONSOLIDATE - fold into another application that covers the same capability. REPLACE - swap for a different product. RETIRE - decommission. This SUPERSEDES the four-term position decided on 2026-08-13 (invest, consolidate, replace, retire, chosen to match the wording of the hackathon prompt itself and of Ryo's REQ 4), under which 'invest' did double duty for both a healthy application kept as it is and one carrying a funded remediation, the two separated only by priority and the REQ 52 pass/fail pattern. That separation was legible inside the engine and not on the page: a steering-committee reader cannot be expected to infer which sense of 'invest' is meant from a priority value, and 'invest' against a healthy application reads as a request for money that nobody is asking for. The engine emits the five terms directly; there is still no mapping layer to any other vocabulary, and slide 13's retain / replace / retire remains a subset of ours rather than a target to map down to. Mechanically the change is small and contained in REQ 52's lookup table: the all-pass key PPPP, previously invest at Very Low priority, now returns retain, and every remaining invest row fails at least one gate, so invest always names the dimension it is funding. The supporting observation from 2026-08-13 still holds - every Info-Tech tool reviewed keeps a consolidate-equivalent (Consolidate, Merge, Absorb, Refocus) while slide 13 does not, and consolidation is where the savings story lives (REQ 25). Requirements carrying this decision: 4 (Ryo's, edited for vocabulary only), 27, 52, 64.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Synthetic data scope</t>
+          <t>Risk in the scoring engine - DECIDED 2026-08-14</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>The overarching prompt describes a 600-application portfolio, so the demo runs on a synthetic portfolio generated to that scale. No client operational data is ingested, used, or committed (see 'Client data - out of scope' below). What must be synthesized, by field category: business-capability tags (REQ 19); active-usage telemetry as distinct from purchased entitlements (REQ 21, 23); most of the per-component TCO breakdown (REQ 20, 55); risk attributes, technical, compliance and clinical (REQ 24, 65); dependency edges and the infrastructure/data footprint (REQ 10, 57); lifecycle stage and sourcing type (REQ 51); retention and archival obligations (REQ 53); and contract terms beyond identifier and end date (REQ 16). Generation rules must be published alongside the data so nothing modelled can be mistaken for measured (REQ 49). Still needs a yes on scale and generation approach before the scoring work starts - it remains the biggest single scope dependency on the sheet.</t>
+          <t>DECIDED by Bina Din on 2026-08-14: risk stays substituted into the borrowed engine's end-user dimension slot. The Info-Tech portfolio tool that REQ 52 borrows its mechanism from scores end-user perception as its fourth dimension; we score risk there instead - REQ 24's technical and business/compliance axes plus REQ 65's clinical and patient-safety axis - so the R in the VTCR key is risk, and a risk failure is a gate failure rather than a footnote. End-user perception is still collected as a field, at integer weight 0, which under REQ 52's renormalisation means it is recorded and reported but never moves a score; a client who wants it scored raises the weight rather than waiting for a rebuild. In a health system an application nobody likes is a training problem, while an application holding PHI on an unpatched host is a board-level one, and only one of those belongs in a gate.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Capability taxonomy</t>
+          <t>Cost in the disposition - DECIDED 2026-08-14</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Requirement 19 assumes we adopt an existing published health-system business capability model rather than authoring one on build day. Bina to confirm which one, since every redundancy finding depends on it.</t>
+          <t>DECIDED by Bina Din on 2026-08-14: cost moves priority, but cost can never on its own make something a retire. Cost efficiency (REQ 23) stays a scored gate and remains a first-order driver of priority and of wave sequencing (REQ 31, REQ 56), so an expensive application surfaces early and loudly. But a cost failure with business value, technical health and risk all passing - the PPFP row of REQ 52's table - resolves to invest, not retire, and no row where cost is the only failure may ever be mapped to retire. An application is retired for lack of value, for being unsupportable, or for carrying unacceptable risk; being expensive makes a decision urgent, not inevitable. Anyone editing the 16-row table has to preserve this.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Demo scope</t>
+          <t>Value dimension weighting - DECIDED 2026-08-14</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Steps 6 and 7 (requirements 37-45) describe post-decision capability, which normally implies a real program running over months. Two of them are demoable on Friday without that: 38 (progress tracking) and 41 (realized vs projected savings) both work by feeding the tool two snapshots of the same portfolio. Worth deciding whether to build one of those, because a tool that closes the loop on whether the savings actually landed is a materially stronger pitch than one that stops at the recommendation.</t>
+          <t>DECIDED by Bina Din on 2026-08-14: inside REQ 21's business value dimension, criticality to patient care takes the double weight (integer weight 2 in REQ 52's per-criterion weighting), and governance and compliance drop to weight 1. Patient-care criticality is the first criterion a clinical stakeholder tests the model against, and it should outweigh a governance attribute rather than sit level with it. Note this is the value dimension only - compliance exposure is still scored at full strength as risk in REQ 24, so lowering its weight here de-duplicates it rather than discounting it, consistent with the one-signal-one-dimension partition below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Cost efficiency benchmark - DECIDED 2026-08-14</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>DECIDED by Bina Din on 2026-08-14: REQ 23's cost efficiency continues to use the modelled peer band - cost per active user compared against the band formed by the other applications carrying the same business capability tag inside the portfolio. That band is modelled, not measured against any external benchmark, published market rate or industry dataset, and every output that uses it must say so under REQ 49's no-silent-inference rule, so a within-portfolio comparison is never read as an industry benchmark. It is a defensible relative signal and an indefensible absolute one, and the outputs have to state which of the two they are.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Reference material</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n"/>
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Synthetic data scope</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>The overarching prompt describes a 600-application portfolio, so the demo runs on a synthetic portfolio generated to that scale. No client operational data is ingested, used, or committed (see 'Client data - out of scope' below). What must be synthesized, by field category: business-capability tags (REQ 19); active-usage telemetry as distinct from purchased entitlements (REQ 21, 23); most of the per-component TCO breakdown (REQ 20, 55); risk attributes, technical, compliance and clinical (REQ 24, 65); dependency edges and the infrastructure/data footprint (REQ 10, 57); lifecycle stage and sourcing type (REQ 51); retention and archival obligations (REQ 53); and contract terms beyond identifier and end date (REQ 16). Generation rules must be published alongside the data so nothing modelled can be mistaken for measured (REQ 49). Still needs a yes on scale and generation approach before the scoring work starts - it remains the biggest single scope dependency on the sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Slide 13 - READ and incorporated</t>
+          <t>Capability taxonomy</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>The seven-step process from slide 13 of Bina's Novant playbook is now the organizing spine of this sheet; every added requirement carries a (Step N) marker and the coverage map above is built from it. Source: the slide-13 image Ryo posted in #hack-team-12 on 2026-08-12, immediately after suggesting we hang AI insertion points off that workflow.</t>
+          <t>Requirement 19 assumes we adopt an existing published health-system business capability model rather than authoring one on build day. Bina to confirm which one, since every redundancy finding depends on it.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Infotech templates - READ 2026-08-13</t>
+          <t>Demo scope</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>All five Info-Tech references Bina shared were read in full on 2026-08-13 (02-Application-Portfolio-Management-Diagnostic-Tool, 02-Build-an-Application-Rationalization-Framework, 04-Rationalize-Your-Application-Portfolio-Tool, 05-Application-TCO-Calculator, 10-Disposition-Prioritization-Tool), which replaces the earlier 'not read' caveat on this row. What they validated: the scoring dimensions behind REQ 21-24 (weighted multi-lens scoring, gates, then disposition plus priority, is still current practice and matches what Gartner TIME, LeanIX, Apptio and ServiceNow APM do today); the TCO component taxonomy now enumerated in REQ 20 and REQ 55; the prioritisation axes in REQ 56; and the disposition mechanism now specified in REQ 52, which is borrowed from the portfolio tool rather than invented. Two genuine obsolescence findings, both of which we have to fix rather than copy: (1) there is no line item anywhere in the reference cost model for consumption or usage-based pricing, which is now the dominant SaaS metric and the primary cost model for the AI tools the prompt calls out - REQ 20 and REQ 55 add it with no precedent to borrow; (2) every scoring input in every template assumes a human fills in a 1-5 grid in a facilitated workshop, which is precisely the step this agent removes - the methodology is current, its data acquisition is a decade behind, and that gap is the pitch (REQ 6-8 derive usage, spend and shadow IT from SSO, AP and contract data instead of asking people). Build caution: the files are internally inconsistent in places - duplicated and misspelled subtotal labels, dropdown lists feeding columns they no longer match, named ranges resolving to #REF!, and one disposition category defined but unreachable from its own lookup table - so nothing was ported without checking it against the file's own cached values, and anything not already written into these requirements should be re-derived rather than copied. Scale note: those tools cap at roughly 500, 25 and 12 records respectively, so they are unusable as tools at 600 applications - only their logic ports. They are licensed third-party vendor material and this repo is public: cite them, never reproduce or commit them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>AI requirements - no external validation</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>None of the reference material mentions AI at all - zero occurrences across all five Info-Tech templates and slide 13's seven-step process. REQ 11 (AI tools and agents as a first-class inventory category), REQ 26 (a capability bought standalone that is already entitled inside an existing enterprise licence) and the consumption-pricing component in REQ 20 and REQ 55 therefore have no external cross-check available: no precedent, no field taxonomy, no scoring rubric. That makes them simultaneously the clearest differentiator on this sheet and the part with the least outside validation, so they need the most internal scrutiny before Friday - someone other than the author should review those requirements specifically.</t>
-        </is>
-      </c>
-    </row>
+          <t>Steps 6 and 7 (requirements 37-45) describe post-decision capability, which normally implies a real program running over months. Two of them are demoable on Friday without that: 38 (progress tracking) and 41 (realized vs projected savings) both work by feeding the tool two snapshots of the same portfolio. Worth deciding whether to build one of those, because a tool that closes the loop on whether the savings actually landed is a materially stronger pitch than one that stops at the recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Dependency guardrail - DECIDED</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>The sheet previously tagged REQ 10 (dependency map) and REQ 29 (breakage and renewal test) STRETCH while REQ 25 (consolidation recommendations) and REQ 27 (disposition assignment) were MVP - so as specified, the Friday tool would recommend retirements and consolidations with no breakage check at all. Of the two available fixes, promote the guardrail or scope consolidation MVP to explicitly disclaim breakage safety, we chose to PROMOTE. REQ 10 now ships an MVP minimum: a per-application has_downstream_dependents boolean plus an enabling / dependent / overlapping flag on each application pair, which is three letters per cell and no formulas. REQ 29's minimum check against that signal, the renewal calendar and REQ 53's retention expiry is MVP too, and REQ 25 now states that every cluster recommendation is checked before it is published. The full confidence-weighted edge list and edge-level deferral scheduling stay STRETCH.</t>
-        </is>
-      </c>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Reference material</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Cost and savings model - corrected</t>
+          <t>Slide 13 - READ and incorporated</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Two arithmetic corrections, both of which move the headline number. (1) REQ 20's component list went from four components to eight: licence and subscription; external support and maintenance; version-upgrade and additional-module fees; internal labour; infrastructure; indirect and training costs; consumption / usage-based charges; and one-time implementation cost held separately from the recurring run-rate. Upgrade and module fees, indirect and training cost, and one-time implementation were all missing, and under-counted cost under-counts savings against the 15% target. REQ 55 carries the published estimation rule for every modelled component. (2) REQ 32 now computes net rather than gross saving - current TCO, minus the replacement or survivor's ongoing TCO, minus amortised one-time migration and implementation cost, minus residual archival and retention cost where a REQ 53 obligation outlives the application - and REQ 54 requires every figure reported both as an annual run-rate and as an undiscounted five-year cumulative. A retire recommendation does not return 100% of an application's cost; in a regulated environment retire is both the disposition most likely to be blocked and the one most likely to leave residual cost behind.</t>
+          <t>The seven-step process from slide 13 of Bina's Novant playbook is now the organizing spine of this sheet; every added requirement carries a (Step N) marker and the coverage map above is built from it. Source: the slide-13 image Ryo posted in #hack-team-12 on 2026-08-12, immediately after suggesting we hang AI insertion points off that workflow.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Scoring input partition</t>
+          <t>Infotech templates - READ 2026-08-13</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Business value (REQ 21), technical health (REQ 22), cost efficiency (REQ 23) and risk (REQ 24) previously shared inputs: unsupported versions and vendor viability were scored in both technical health and risk, so one obsolescence fact failed two of the four gates and the engine systematically over-recommended retiring old-but-adequate applications. Every signal now belongs to exactly one dimension, stated in the text of each requirement so the partition survives into the build. REQ 22 owns version currency, EOL proximity, unsupported-version status, architecture fit, operational stability and vendor viability. REQ 24 owns single points of failure, absent DR or backup, single-vendor concentration, unhardened configuration, PHI and HIPAA exposure, data residency, SOC 2 / HITRUST posture and contractual lock-in. REQ 65 owns the clinical and patient-safety axis. REQ 23 owns the cost signals. REQ 21 owns criticality, usage breadth, process centrality and owner-stated strategic importance.</t>
+          <t>All five Info-Tech references Bina shared were read in full on 2026-08-13 (02-Application-Portfolio-Management-Diagnostic-Tool, 02-Build-an-Application-Rationalization-Framework, 04-Rationalize-Your-Application-Portfolio-Tool, 05-Application-TCO-Calculator, 10-Disposition-Prioritization-Tool), which replaces the earlier 'not read' caveat on this row. What they validated: the scoring dimensions behind REQ 21-24 (weighted multi-lens scoring, gates, then disposition plus priority, is still current practice and matches what Gartner TIME, LeanIX, Apptio and ServiceNow APM do today); the TCO component taxonomy now enumerated in REQ 20 and REQ 55; the prioritisation axes in REQ 56; and the disposition mechanism now specified in REQ 52, which is borrowed from the portfolio tool rather than invented. Two genuine obsolescence findings, both of which we have to fix rather than copy: (1) there is no line item anywhere in the reference cost model for consumption or usage-based pricing, which is now the dominant SaaS metric and the primary cost model for the AI tools the prompt calls out - REQ 20 and REQ 55 add it with no precedent to borrow; (2) every scoring input in every template assumes a human fills in a 1-5 grid in a facilitated workshop, which is precisely the step this agent removes - the methodology is current, its data acquisition is a decade behind, and that gap is the pitch (REQ 6-8 derive usage, spend and shadow IT from SSO, AP and contract data instead of asking people). Build caution: the files are internally inconsistent in places - duplicated and misspelled subtotal labels, dropdown lists feeding columns they no longer match, named ranges resolving to #REF!, and one disposition category defined but unreachable from its own lookup table - so nothing was ported without checking it against the file's own cached values, and anything not already written into these requirements should be re-derived rather than copied. Scale note: those tools cap at roughly 500, 25 and 12 records respectively, so they are unusable as tools at 600 applications - only their logic ports. They are licensed third-party vendor material and this repo is public: cite them, never reproduce or commit them.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Disposition engine - specified</t>
+          <t>AI requirements - no external validation</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>REQ 52 pins the mechanism the sheet previously left open, concretely enough to code: gate REQ 21, 22, 23 and 24 at 3.0 on the 1-5 scale, concatenate the four pass/fail results into a VTCR key, look that key up in a 16-row editable table returning one of the four agreed dispositions plus a priority (Very High through Very Low), store the key as the human-readable rationale skeleton REQ 27 needs, force consolidate wherever REQ 25 finds cluster membership, apply REQ 51's lifecycle and sourcing exclusions after the lookup and record every suppression with its reason, and allow the REQ 30 human override validated against the same four terms. The default 16-row mapping is written into REQ 52 and is configuration rather than code, which means a client can argue with the table directly instead of with a black box. Note also that the value-by-health 2x2 in REQ 4 and REQ 27 remains the right chart but cannot be the engine: a 2x2 has no axis on which 'consolidate' can appear, and consolidate is where the savings are.</t>
+          <t>None of the reference material mentions AI at all - zero occurrences across all five Info-Tech templates and slide 13's seven-step process. REQ 11 (AI tools and agents as a first-class inventory category), REQ 26 (a capability bought standalone that is already entitled inside an existing enterprise licence) and the consumption-pricing component in REQ 20 and REQ 55 therefore have no external cross-check available: no precedent, no field taxonomy, no scoring rubric. That makes them simultaneously the clearest differentiator on this sheet and the part with the least outside validation, so they need the most internal scrutiny before Friday - someone other than the author should review those requirements specifically.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
+          <t>Dependency guardrail - DECIDED</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>The sheet previously tagged REQ 10 (dependency map) and REQ 29 (breakage and renewal test) STRETCH while REQ 25 (consolidation recommendations) and REQ 27 (disposition assignment) were MVP - so as specified, the Friday tool would recommend retirements and consolidations with no breakage check at all. Of the two available fixes, promote the guardrail or scope consolidation MVP to explicitly disclaim breakage safety, we chose to PROMOTE. REQ 10 now ships an MVP minimum: a per-application has_downstream_dependents boolean plus an enabling / dependent / overlapping flag on each application pair, which is three letters per cell and no formulas. REQ 29's minimum check against that signal, the renewal calendar and REQ 53's retention expiry is MVP too, and REQ 25 now states that every cluster recommendation is checked before it is published. The full confidence-weighted edge list and edge-level deferral scheduling stay STRETCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Cost and savings model - corrected</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Two arithmetic corrections, both of which move the headline number. (1) REQ 20's component list went from four components to eight: licence and subscription; external support and maintenance; version-upgrade and additional-module fees; internal labour; infrastructure; indirect and training costs; consumption / usage-based charges; and one-time implementation cost held separately from the recurring run-rate. Upgrade and module fees, indirect and training cost, and one-time implementation were all missing, and under-counted cost under-counts savings against the 15% target. REQ 55 carries the published estimation rule for every modelled component. (2) REQ 32 now computes net rather than gross saving - current TCO, minus the replacement or survivor's ongoing TCO, minus amortised one-time migration and implementation cost, minus residual archival and retention cost where a REQ 53 obligation outlives the application - and REQ 54 requires every figure reported both as an annual run-rate and as an undiscounted five-year cumulative. A retire recommendation does not return 100% of an application's cost; in a regulated environment retire is both the disposition most likely to be blocked and the one most likely to leave residual cost behind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Scoring input partition</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Business value (REQ 21), technical health (REQ 22), cost efficiency (REQ 23) and risk (REQ 24) previously shared inputs: unsupported versions and vendor viability were scored in both technical health and risk, so one obsolescence fact failed two of the four gates and the engine systematically over-recommended retiring old-but-adequate applications. Every signal now belongs to exactly one dimension, stated in the text of each requirement so the partition survives into the build. REQ 22 owns version currency, EOL proximity, unsupported-version status, architecture fit, operational stability and vendor viability. REQ 24 owns single points of failure, absent DR or backup, single-vendor concentration, unhardened configuration, PHI and HIPAA exposure, data residency, SOC 2 / HITRUST posture and contractual lock-in. REQ 65 owns the clinical and patient-safety axis. REQ 23 owns the cost signals. REQ 21 owns criticality, usage breadth, process centrality and owner-stated strategic importance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Disposition engine - specified</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>REQ 52 pins the mechanism the sheet previously left open, concretely enough to code: gate REQ 21, 22, 23 and 24 at 3.0 on the 1-5 scale, concatenate the four pass/fail results into a VTCR key, look that key up in a 16-row editable table returning one of the five agreed dispositions plus a priority (Very High through Very Low), the all-pass key PPPP returning retain since 2026-08-14 while every invest row fails at least one gate, store the key as the human-readable rationale skeleton REQ 27 needs, force consolidate wherever REQ 25 finds cluster membership, apply REQ 51's lifecycle and sourcing exclusions after the lookup and record every suppression with its reason, and allow the REQ 30 human override validated against the same five terms. The default 16-row mapping is written into REQ 52 and is configuration rather than code, which means a client can argue with the table directly instead of with a black box. Note also that the value-by-health 2x2 in REQ 4 and REQ 27 remains the right chart but cannot be the engine: a 2x2 has no axis on which 'consolidate' can appear, and consolidate is where the savings are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
           <t>Client data - out of scope</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Bina ruled client operational data out of scope on 2026-08-13. Nothing in this workbook derives from it: no application inventory, no named individuals, no contract identifiers, no cost or contract actuals, no server names, and no departments or legal entities appear anywhere in these requirements, and none may be added. This repository is public, which means there is no access-control boundary of any kind and git history is permanent, so the same standard applies to every file committed here - generic methodology and field names are in scope, client content is not. The demo runs on the synthetic portfolio described above.</t>
         </is>

--- a/docs/requirements/Application Rationalization Agent Requirements - filled.xlsx
+++ b/docs/requirements/Application Rationalization Agent Requirements - filled.xlsx
@@ -1450,7 +1450,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>(Step 3) Roll the per-application scores up to a business-capability view: for each capability, average the dimension scores of every application mapped to it, apply configurable per-dimension weightings that must total 100%, and band the result as Strong (above 75%), Improve (50-75%), Remediate (25-50%) or Critical Need (0-25%). Report capability coverage alongside capability spend and application count, so the portfolio can be read as 'where are we over-invested and under-served' rather than only as a list of per-application verdicts. This is a second analysis mode distinct from per-application disposition, and it is the natural executive view. [MVP for the rollup and the bands; STRETCH for configurable weightings] [REF: Infotech 04-Rationalize-Your-Application-Portfolio-Tool - Group 1/2/3 Results, its capability weighting rows and its four performance bands]</t>
+          <t>(Step 3) Roll the per-application scores up to a business-capability view: for each capability, average the dimension scores of every application mapped to it, apply configurable per-dimension weightings that must total 100%, and band the result into four performance bands on the same percentage boundaries (above 75%, 50-75%, 25-50%, 0-25%), labelled in our own words rather than the reference tool's. Report capability coverage alongside capability spend and application count, so the portfolio can be read as 'where are we over-invested and under-served' rather than only as a list of per-application verdicts. This is a second analysis mode distinct from per-application disposition, and it is the natural executive view. [MVP for the rollup and the bands; STRETCH for configurable weightings] [REF: Infotech 04-Rationalize-Your-Application-Portfolio-Tool - Group 1/2/3 Results, its capability weighting rows and its four performance bands]</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>DECIDED by Bina Din on 2026-08-14: the disposition vocabulary is five terms - retain, invest, consolidate, replace, retire. Asked to confirm that the four-term version read correctly in front of a steering committee, her answer was: 'No, separate by invest, retain, consolidate, replace, and retire.' Definitions, to be used exactly as written in every output: RETAIN - healthy, leave alone, no new spend. INVEST - fund a remediation or enhancement; a deliberate injection of money or effort. CONSOLIDATE - fold into another application that covers the same capability. REPLACE - swap for a different product. RETIRE - decommission. This SUPERSEDES the four-term position decided on 2026-08-13 (invest, consolidate, replace, retire, chosen to match the wording of the hackathon prompt itself and of Ryo's REQ 4), under which 'invest' did double duty for both a healthy application kept as it is and one carrying a funded remediation, the two separated only by priority and the REQ 52 pass/fail pattern. That separation was legible inside the engine and not on the page: a steering-committee reader cannot be expected to infer which sense of 'invest' is meant from a priority value, and 'invest' against a healthy application reads as a request for money that nobody is asking for. The engine emits the five terms directly; there is still no mapping layer to any other vocabulary, and slide 13's retain / replace / retire remains a subset of ours rather than a target to map down to. Mechanically the change is small and contained in REQ 52's lookup table: the all-pass key PPPP, previously invest at Very Low priority, now returns retain, and every remaining invest row fails at least one gate, so invest always names the dimension it is funding. The supporting observation from 2026-08-13 still holds - every Info-Tech tool reviewed keeps a consolidate-equivalent (Consolidate, Merge, Absorb, Refocus) while slide 13 does not, and consolidation is where the savings story lives (REQ 25). Requirements carrying this decision: 4 (Ryo's, edited for vocabulary only), 27, 52, 64.</t>
+          <t>DECIDED by Bina Din on 2026-08-14: the disposition vocabulary is five terms - retain, invest, consolidate, replace, retire. Asked to confirm that the four-term version read correctly in front of a steering committee, her answer was: 'No, separate by invest, retain, consolidate, replace, and retire.' Definitions, to be used exactly as written in every output: RETAIN - healthy, leave alone, no new spend. INVEST - fund a remediation or enhancement; a deliberate injection of money or effort. CONSOLIDATE - fold into another application that covers the same capability. REPLACE - swap for a different product. RETIRE - decommission. This SUPERSEDES the four-term position decided on 2026-08-13 (invest, consolidate, replace, retire, chosen to match the wording of the hackathon prompt itself and of Ryo's REQ 4), under which 'invest' did double duty for both a healthy application kept as it is and one carrying a funded remediation, the two separated only by priority and the REQ 52 pass/fail pattern. That separation was legible inside the engine and not on the page: a steering-committee reader cannot be expected to infer which sense of 'invest' is meant from a priority value, and 'invest' against a healthy application reads as a request for money that nobody is asking for. The engine emits the five terms directly; there is still no mapping layer to any other vocabulary, and slide 13's retain / replace / retire remains a subset of ours rather than a target to map down to. Mechanically the change is small and contained in REQ 52's lookup table: the all-pass key PPPP, previously invest at Very Low priority, now returns retain, and every remaining invest row fails at least one gate, so invest always names the dimension it is funding. The supporting observation from 2026-08-13 still holds - every Info-Tech tool reviewed keeps a consolidate-equivalent term in its own vocabulary while slide 13 does not, and consolidation is where the savings story lives (REQ 25). Requirements carrying this decision: 4 (Ryo's, edited for vocabulary only), 27, 52, 64.</t>
         </is>
       </c>
     </row>
